--- a/research/traditional_assets/database/data/zambia/zambia_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/zambia/zambia_electrical_equipment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2258110045850647</v>
+        <v>0.225049916069017</v>
       </c>
       <c r="C2">
-        <v>34.04874973228353</v>
+        <v>33.75169950992841</v>
       </c>
       <c r="D2">
-        <v>20.14874973228353</v>
+        <v>20.20019950992842</v>
       </c>
       <c r="E2">
-        <v>-30</v>
+        <v>-29.6515</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3485</v>
       </c>
       <c r="G2">
         <v>13.9</v>
@@ -1439,28 +1439,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01752955</v>
       </c>
       <c r="N2">
-        <v>10.71632653061224</v>
+        <v>10.69879698061224</v>
       </c>
       <c r="O2">
-        <v>3.750714285714285</v>
+        <v>3.744578943214285</v>
       </c>
       <c r="P2">
-        <v>6.965612244897959</v>
+        <v>6.954218037397959</v>
       </c>
       <c r="Q2">
-        <v>7.065612244897959</v>
+        <v>7.054218037397958</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2258110045850647</v>
+        <v>0.2269928950192091</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.10815319019043</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>611.3292429419034</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.225049916069017</v>
+        <v>0.2242888275529693</v>
       </c>
       <c r="C3">
-        <v>33.75169950992841</v>
+        <v>33.45491271396646</v>
       </c>
       <c r="D3">
-        <v>20.20019950992842</v>
+        <v>20.25191271396647</v>
       </c>
       <c r="E3">
-        <v>-29.6515</v>
+        <v>-29.303</v>
       </c>
       <c r="F3">
-        <v>0.3485</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="G3">
         <v>13.9</v>
@@ -1521,28 +1521,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M3">
-        <v>0.01752955</v>
+        <v>0.0350591</v>
       </c>
       <c r="N3">
-        <v>10.69879698061224</v>
+        <v>10.68126743061224</v>
       </c>
       <c r="O3">
-        <v>3.744578943214285</v>
+        <v>3.738443600714285</v>
       </c>
       <c r="P3">
-        <v>6.954218037397959</v>
+        <v>6.942823829897959</v>
       </c>
       <c r="Q3">
-        <v>7.054218037397958</v>
+        <v>7.042823829897959</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2269928950192091</v>
+        <v>0.2281989056662952</v>
       </c>
       <c r="T3">
-        <v>1.10815319019043</v>
+        <v>1.115529001178109</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>611.3292429419034</v>
+        <v>305.6646214709517</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2242888275529693</v>
+        <v>0.2235277390369215</v>
       </c>
       <c r="C4">
-        <v>33.45491271396646</v>
+        <v>33.15839137273213</v>
       </c>
       <c r="D4">
-        <v>20.25191271396647</v>
+        <v>20.30389137273212</v>
       </c>
       <c r="E4">
-        <v>-29.303</v>
+        <v>-28.9545</v>
       </c>
       <c r="F4">
-        <v>0.6970000000000001</v>
+        <v>1.0455</v>
       </c>
       <c r="G4">
         <v>13.9</v>
@@ -1603,28 +1603,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M4">
-        <v>0.0350591</v>
+        <v>0.05258865</v>
       </c>
       <c r="N4">
-        <v>10.68126743061224</v>
+        <v>10.66373788061224</v>
       </c>
       <c r="O4">
-        <v>3.738443600714285</v>
+        <v>3.732308258214285</v>
       </c>
       <c r="P4">
-        <v>6.942823829897959</v>
+        <v>6.931429622397959</v>
       </c>
       <c r="Q4">
-        <v>7.042823829897959</v>
+        <v>7.031429622397958</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2281989056662952</v>
+        <v>0.2294297825122902</v>
       </c>
       <c r="T4">
-        <v>1.115529001178109</v>
+        <v>1.123056890742854</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>305.6646214709517</v>
+        <v>203.7764143139678</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2235277390369215</v>
+        <v>0.2227666505208738</v>
       </c>
       <c r="C5">
-        <v>33.15839137273213</v>
+        <v>32.86213753543711</v>
       </c>
       <c r="D5">
-        <v>20.30389137273212</v>
+        <v>20.35613753543711</v>
       </c>
       <c r="E5">
-        <v>-28.9545</v>
+        <v>-28.606</v>
       </c>
       <c r="F5">
-        <v>1.0455</v>
+        <v>1.394</v>
       </c>
       <c r="G5">
         <v>13.9</v>
@@ -1685,28 +1685,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M5">
-        <v>0.05258865</v>
+        <v>0.07011820000000001</v>
       </c>
       <c r="N5">
-        <v>10.66373788061224</v>
+        <v>10.64620833061224</v>
       </c>
       <c r="O5">
-        <v>3.732308258214285</v>
+        <v>3.726172915714285</v>
       </c>
       <c r="P5">
-        <v>6.931429622397959</v>
+        <v>6.92003541489796</v>
       </c>
       <c r="Q5">
-        <v>7.031429622397958</v>
+        <v>7.02003541489796</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2294297825122902</v>
+        <v>0.2306863026259102</v>
       </c>
       <c r="T5">
-        <v>1.123056890742854</v>
+        <v>1.130741611340197</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>203.7764143139678</v>
+        <v>152.8323107354759</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2227666505208738</v>
+        <v>0.2220055620048261</v>
       </c>
       <c r="C6">
-        <v>32.86213753543711</v>
+        <v>32.56615327243981</v>
       </c>
       <c r="D6">
-        <v>20.35613753543711</v>
+        <v>20.4086532724398</v>
       </c>
       <c r="E6">
-        <v>-28.606</v>
+        <v>-28.2575</v>
       </c>
       <c r="F6">
-        <v>1.394</v>
+        <v>1.7425</v>
       </c>
       <c r="G6">
         <v>13.9</v>
@@ -1767,28 +1767,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M6">
-        <v>0.07011820000000001</v>
+        <v>0.08764775000000001</v>
       </c>
       <c r="N6">
-        <v>10.64620833061224</v>
+        <v>10.62867878061224</v>
       </c>
       <c r="O6">
-        <v>3.726172915714285</v>
+        <v>3.720037573214285</v>
       </c>
       <c r="P6">
-        <v>6.92003541489796</v>
+        <v>6.90864120739796</v>
       </c>
       <c r="Q6">
-        <v>7.02003541489796</v>
+        <v>7.008641207397959</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2306863026259102</v>
+        <v>0.2319692757945538</v>
       </c>
       <c r="T6">
-        <v>1.130741611340197</v>
+        <v>1.138588115529064</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>152.8323107354759</v>
+        <v>122.2658485883807</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2220055620048261</v>
+        <v>0.2212444734887784</v>
       </c>
       <c r="C7">
-        <v>32.56615327243981</v>
+        <v>32.27044067551866</v>
       </c>
       <c r="D7">
-        <v>20.4086532724398</v>
+        <v>20.46144067551866</v>
       </c>
       <c r="E7">
-        <v>-28.2575</v>
+        <v>-27.909</v>
       </c>
       <c r="F7">
-        <v>1.7425</v>
+        <v>2.091</v>
       </c>
       <c r="G7">
         <v>13.9</v>
@@ -1849,28 +1849,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M7">
-        <v>0.08764775000000001</v>
+        <v>0.1051773</v>
       </c>
       <c r="N7">
-        <v>10.62867878061224</v>
+        <v>10.61114923061225</v>
       </c>
       <c r="O7">
-        <v>3.720037573214285</v>
+        <v>3.713902230714285</v>
       </c>
       <c r="P7">
-        <v>6.90864120739796</v>
+        <v>6.897246999897959</v>
       </c>
       <c r="Q7">
-        <v>7.008641207397959</v>
+        <v>6.997246999897959</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2319692757945538</v>
+        <v>0.2332795462646579</v>
       </c>
       <c r="T7">
-        <v>1.138588115529064</v>
+        <v>1.146601566615566</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>122.2658485883807</v>
+        <v>101.8882071569839</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2212444734887784</v>
+        <v>0.2204833849727307</v>
       </c>
       <c r="C8">
-        <v>32.27044067551866</v>
+        <v>31.97500185814997</v>
       </c>
       <c r="D8">
-        <v>20.46144067551866</v>
+        <v>20.51450185814997</v>
       </c>
       <c r="E8">
-        <v>-27.909</v>
+        <v>-27.5605</v>
       </c>
       <c r="F8">
-        <v>2.091</v>
+        <v>2.4395</v>
       </c>
       <c r="G8">
         <v>13.9</v>
@@ -1931,28 +1931,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M8">
-        <v>0.1051773</v>
+        <v>0.12270685</v>
       </c>
       <c r="N8">
-        <v>10.61114923061225</v>
+        <v>10.59361968061224</v>
       </c>
       <c r="O8">
-        <v>3.713902230714285</v>
+        <v>3.707766888214285</v>
       </c>
       <c r="P8">
-        <v>6.897246999897959</v>
+        <v>6.885852792397959</v>
       </c>
       <c r="Q8">
-        <v>6.997246999897959</v>
+        <v>6.985852792397958</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2332795462646579</v>
+        <v>0.234617994594334</v>
       </c>
       <c r="T8">
-        <v>1.146601566615566</v>
+        <v>1.154787349983498</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>101.8882071569839</v>
+        <v>87.33274899170051</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2204833849727306</v>
+        <v>0.2197222964566829</v>
       </c>
       <c r="C9">
-        <v>31.97500185814997</v>
+        <v>31.67983895578994</v>
       </c>
       <c r="D9">
-        <v>20.51450185814997</v>
+        <v>20.56783895578993</v>
       </c>
       <c r="E9">
-        <v>-27.5605</v>
+        <v>-27.212</v>
       </c>
       <c r="F9">
-        <v>2.4395</v>
+        <v>2.788</v>
       </c>
       <c r="G9">
         <v>13.9</v>
@@ -2013,28 +2013,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M9">
-        <v>0.12270685</v>
+        <v>0.1402364</v>
       </c>
       <c r="N9">
-        <v>10.59361968061224</v>
+        <v>10.57609013061225</v>
       </c>
       <c r="O9">
-        <v>3.707766888214285</v>
+        <v>3.701631545714286</v>
       </c>
       <c r="P9">
-        <v>6.885852792397959</v>
+        <v>6.87445858489796</v>
       </c>
       <c r="Q9">
-        <v>6.985852792397958</v>
+        <v>6.97445858489796</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.234617994594334</v>
+        <v>0.2359855396268292</v>
       </c>
       <c r="T9">
-        <v>1.154787349983498</v>
+        <v>1.163151085163776</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>87.3327489917005</v>
+        <v>76.41615536773794</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2197222964566829</v>
+        <v>0.2189612079406352</v>
       </c>
       <c r="C10">
-        <v>31.67983895578994</v>
+        <v>31.38495412616115</v>
       </c>
       <c r="D10">
-        <v>20.56783895578993</v>
+        <v>20.62145412616115</v>
       </c>
       <c r="E10">
-        <v>-27.212</v>
+        <v>-26.8635</v>
       </c>
       <c r="F10">
-        <v>2.788</v>
+        <v>3.1365</v>
       </c>
       <c r="G10">
         <v>13.9</v>
@@ -2095,28 +2095,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M10">
-        <v>0.1402364</v>
+        <v>0.15776595</v>
       </c>
       <c r="N10">
-        <v>10.57609013061225</v>
+        <v>10.55856058061224</v>
       </c>
       <c r="O10">
-        <v>3.701631545714286</v>
+        <v>3.695496203214285</v>
       </c>
       <c r="P10">
-        <v>6.87445858489796</v>
+        <v>6.86306437739796</v>
       </c>
       <c r="Q10">
-        <v>6.97445858489796</v>
+        <v>6.963064377397959</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2359855396268292</v>
+        <v>0.2373831405941046</v>
       </c>
       <c r="T10">
-        <v>1.163151085163776</v>
+        <v>1.171698638699665</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>76.41615536773794</v>
+        <v>67.92547143798929</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2189612079406352</v>
+        <v>0.2182001194245875</v>
       </c>
       <c r="C11">
-        <v>31.38495412616115</v>
+        <v>31.09034954954353</v>
       </c>
       <c r="D11">
-        <v>20.62145412616115</v>
+        <v>20.67534954954353</v>
       </c>
       <c r="E11">
-        <v>-26.8635</v>
+        <v>-26.515</v>
       </c>
       <c r="F11">
-        <v>3.1365</v>
+        <v>3.485</v>
       </c>
       <c r="G11">
         <v>13.9</v>
@@ -2177,28 +2177,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M11">
-        <v>0.15776595</v>
+        <v>0.1752955</v>
       </c>
       <c r="N11">
-        <v>10.55856058061224</v>
+        <v>10.54103103061224</v>
       </c>
       <c r="O11">
-        <v>3.695496203214285</v>
+        <v>3.689360860714285</v>
       </c>
       <c r="P11">
-        <v>6.86306437739796</v>
+        <v>6.851670169897959</v>
       </c>
       <c r="Q11">
-        <v>6.963064377397959</v>
+        <v>6.951670169897959</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2373831405941046</v>
+        <v>0.2388117993606527</v>
       </c>
       <c r="T11">
-        <v>1.171698638699665</v>
+        <v>1.180436137869685</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>67.92547143798929</v>
+        <v>61.13292429419035</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2182001194245875</v>
+        <v>0.2174390309085398</v>
       </c>
       <c r="C12">
-        <v>31.09034954954353</v>
+        <v>30.79602742906994</v>
       </c>
       <c r="D12">
-        <v>20.67534954954353</v>
+        <v>20.72952742906994</v>
       </c>
       <c r="E12">
-        <v>-26.515</v>
+        <v>-26.1665</v>
       </c>
       <c r="F12">
-        <v>3.485</v>
+        <v>3.8335</v>
       </c>
       <c r="G12">
         <v>13.9</v>
@@ -2259,28 +2259,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M12">
-        <v>0.1752955</v>
+        <v>0.19282505</v>
       </c>
       <c r="N12">
-        <v>10.54103103061224</v>
+        <v>10.52350148061224</v>
       </c>
       <c r="O12">
-        <v>3.689360860714285</v>
+        <v>3.683225518214285</v>
       </c>
       <c r="P12">
-        <v>6.851670169897959</v>
+        <v>6.840275962397959</v>
       </c>
       <c r="Q12">
-        <v>6.951670169897959</v>
+        <v>6.940275962397958</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2388117993606527</v>
+        <v>0.240272562818584</v>
       </c>
       <c r="T12">
-        <v>1.180436137869685</v>
+        <v>1.189369985335661</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>61.13292429419034</v>
+        <v>55.57538572199123</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2174390309085398</v>
+        <v>0.216677942392492</v>
       </c>
       <c r="C13">
-        <v>30.79602742906994</v>
+        <v>30.50198999102633</v>
       </c>
       <c r="D13">
-        <v>20.72952742906994</v>
+        <v>20.78398999102633</v>
       </c>
       <c r="E13">
-        <v>-26.1665</v>
+        <v>-25.818</v>
       </c>
       <c r="F13">
-        <v>3.8335</v>
+        <v>4.182</v>
       </c>
       <c r="G13">
         <v>13.9</v>
@@ -2341,28 +2341,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M13">
-        <v>0.19282505</v>
+        <v>0.2103546</v>
       </c>
       <c r="N13">
-        <v>10.52350148061224</v>
+        <v>10.50597193061224</v>
       </c>
       <c r="O13">
-        <v>3.683225518214285</v>
+        <v>3.677090175714285</v>
       </c>
       <c r="P13">
-        <v>6.840275962397959</v>
+        <v>6.828881754897958</v>
       </c>
       <c r="Q13">
-        <v>6.940275962397958</v>
+        <v>6.928881754897958</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.240272562818584</v>
+        <v>0.2417665254460137</v>
       </c>
       <c r="T13">
-        <v>1.189369985335661</v>
+        <v>1.198506874789499</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>55.57538572199123</v>
+        <v>50.94410357849195</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.216677942392492</v>
+        <v>0.2159168538764443</v>
       </c>
       <c r="C14">
-        <v>30.50198999102633</v>
+        <v>30.20823948515671</v>
       </c>
       <c r="D14">
-        <v>20.78398999102633</v>
+        <v>20.83873948515671</v>
       </c>
       <c r="E14">
-        <v>-25.818</v>
+        <v>-25.4695</v>
       </c>
       <c r="F14">
-        <v>4.182</v>
+        <v>4.5305</v>
       </c>
       <c r="G14">
         <v>13.9</v>
@@ -2423,28 +2423,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M14">
-        <v>0.2103546</v>
+        <v>0.22788415</v>
       </c>
       <c r="N14">
-        <v>10.50597193061224</v>
+        <v>10.48844238061224</v>
       </c>
       <c r="O14">
-        <v>3.677090175714285</v>
+        <v>3.670954833214286</v>
       </c>
       <c r="P14">
-        <v>6.828881754897958</v>
+        <v>6.81748754739796</v>
       </c>
       <c r="Q14">
-        <v>6.928881754897958</v>
+        <v>6.917487547397959</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2417665254460137</v>
+        <v>0.24329483204189</v>
       </c>
       <c r="T14">
-        <v>1.198506874789499</v>
+        <v>1.207853807679058</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>50.94410357849195</v>
+        <v>47.02532638014643</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2159168538764443</v>
+        <v>0.2151557653603966</v>
       </c>
       <c r="C15">
-        <v>30.20823948515671</v>
+        <v>29.91477818497293</v>
       </c>
       <c r="D15">
-        <v>20.83873948515671</v>
+        <v>20.89377818497293</v>
       </c>
       <c r="E15">
-        <v>-25.4695</v>
+        <v>-25.121</v>
       </c>
       <c r="F15">
-        <v>4.5305</v>
+        <v>4.879</v>
       </c>
       <c r="G15">
         <v>13.9</v>
@@ -2505,28 +2505,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M15">
-        <v>0.22788415</v>
+        <v>0.2454137</v>
       </c>
       <c r="N15">
-        <v>10.48844238061224</v>
+        <v>10.47091283061224</v>
       </c>
       <c r="O15">
-        <v>3.670954833214286</v>
+        <v>3.664819490714285</v>
       </c>
       <c r="P15">
-        <v>6.81748754739796</v>
+        <v>6.806093339897959</v>
       </c>
       <c r="Q15">
-        <v>6.917487547397959</v>
+        <v>6.906093339897959</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.24329483204189</v>
+        <v>0.2448586806516239</v>
       </c>
       <c r="T15">
-        <v>1.207853807679058</v>
+        <v>1.217418111100932</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>47.02532638014643</v>
+        <v>43.66637449585025</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2151557653603966</v>
+        <v>0.2143946768443488</v>
       </c>
       <c r="C16">
-        <v>29.91477818497293</v>
+        <v>29.62160838806943</v>
       </c>
       <c r="D16">
-        <v>20.89377818497293</v>
+        <v>20.94910838806942</v>
       </c>
       <c r="E16">
-        <v>-25.121</v>
+        <v>-24.7725</v>
       </c>
       <c r="F16">
-        <v>4.879</v>
+        <v>5.227500000000001</v>
       </c>
       <c r="G16">
         <v>13.9</v>
@@ -2587,28 +2587,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M16">
-        <v>0.2454137</v>
+        <v>0.26294325</v>
       </c>
       <c r="N16">
-        <v>10.47091283061224</v>
+        <v>10.45338328061225</v>
       </c>
       <c r="O16">
-        <v>3.664819490714285</v>
+        <v>3.658684148214285</v>
       </c>
       <c r="P16">
-        <v>6.806093339897959</v>
+        <v>6.79469913239796</v>
       </c>
       <c r="Q16">
-        <v>6.906093339897959</v>
+        <v>6.894699132397959</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2448586806516239</v>
+        <v>0.2464593256992339</v>
       </c>
       <c r="T16">
-        <v>1.217418111100932</v>
+        <v>1.227207456956262</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>43.66637449585025</v>
+        <v>40.75528286279356</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2143946768443488</v>
+        <v>0.2136335883283011</v>
       </c>
       <c r="C17">
-        <v>29.62160838806943</v>
+        <v>29.32873241644286</v>
       </c>
       <c r="D17">
-        <v>20.94910838806942</v>
+        <v>21.00473241644286</v>
       </c>
       <c r="E17">
-        <v>-24.7725</v>
+        <v>-24.424</v>
       </c>
       <c r="F17">
-        <v>5.2275</v>
+        <v>5.576000000000001</v>
       </c>
       <c r="G17">
         <v>13.9</v>
@@ -2669,28 +2669,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M17">
-        <v>0.26294325</v>
+        <v>0.2804728</v>
       </c>
       <c r="N17">
-        <v>10.45338328061225</v>
+        <v>10.43585373061224</v>
       </c>
       <c r="O17">
-        <v>3.658684148214285</v>
+        <v>3.652548805714285</v>
       </c>
       <c r="P17">
-        <v>6.79469913239796</v>
+        <v>6.783304924897958</v>
       </c>
       <c r="Q17">
-        <v>6.894699132397959</v>
+        <v>6.883304924897958</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2464593256992339</v>
+        <v>0.2480980813432156</v>
       </c>
       <c r="T17">
-        <v>1.227207456956262</v>
+        <v>1.237229882474814</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>40.75528286279358</v>
+        <v>38.20807768386896</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2136335883283011</v>
+        <v>0.2128724998122534</v>
       </c>
       <c r="C18">
-        <v>29.32873241644286</v>
+        <v>29.03615261681701</v>
       </c>
       <c r="D18">
-        <v>21.00473241644286</v>
+        <v>21.06065261681702</v>
       </c>
       <c r="E18">
-        <v>-24.424</v>
+        <v>-24.0755</v>
       </c>
       <c r="F18">
-        <v>5.576000000000001</v>
+        <v>5.924500000000001</v>
       </c>
       <c r="G18">
         <v>13.9</v>
@@ -2751,28 +2751,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M18">
-        <v>0.2804728</v>
+        <v>0.29800235</v>
       </c>
       <c r="N18">
-        <v>10.43585373061224</v>
+        <v>10.41832418061224</v>
       </c>
       <c r="O18">
-        <v>3.652548805714285</v>
+        <v>3.646413463214285</v>
       </c>
       <c r="P18">
-        <v>6.783304924897958</v>
+        <v>6.771910717397958</v>
       </c>
       <c r="Q18">
-        <v>6.883304924897958</v>
+        <v>6.871910717397958</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2480980813432156</v>
+        <v>0.2497763250750041</v>
       </c>
       <c r="T18">
-        <v>1.237229882474814</v>
+        <v>1.247493812222729</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>38.20807768386896</v>
+        <v>35.9605437024649</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2128724998122534</v>
+        <v>0.2121114112962056</v>
       </c>
       <c r="C19">
-        <v>29.03615261681701</v>
+        <v>28.74387136097282</v>
       </c>
       <c r="D19">
-        <v>21.06065261681702</v>
+        <v>21.11687136097282</v>
       </c>
       <c r="E19">
-        <v>-24.0755</v>
+        <v>-23.727</v>
       </c>
       <c r="F19">
-        <v>5.924500000000001</v>
+        <v>6.273000000000001</v>
       </c>
       <c r="G19">
         <v>13.9</v>
@@ -2833,28 +2833,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M19">
-        <v>0.29800235</v>
+        <v>0.3155319</v>
       </c>
       <c r="N19">
-        <v>10.41832418061224</v>
+        <v>10.40079463061224</v>
       </c>
       <c r="O19">
-        <v>3.646413463214285</v>
+        <v>3.640278120714285</v>
       </c>
       <c r="P19">
-        <v>6.771910717397958</v>
+        <v>6.760516509897959</v>
       </c>
       <c r="Q19">
-        <v>6.871910717397958</v>
+        <v>6.860516509897959</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2497763250750041</v>
+        <v>0.2514955015807386</v>
       </c>
       <c r="T19">
-        <v>1.247493812222729</v>
+        <v>1.258008081720593</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>35.9605437024649</v>
+        <v>33.96273571899464</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2121114112962056</v>
+        <v>0.2113503227801579</v>
       </c>
       <c r="C20">
-        <v>28.74387136097282</v>
+        <v>28.45189104608361</v>
       </c>
       <c r="D20">
-        <v>21.11687136097282</v>
+        <v>21.17339104608362</v>
       </c>
       <c r="E20">
-        <v>-23.727</v>
+        <v>-23.3785</v>
       </c>
       <c r="F20">
-        <v>6.273</v>
+        <v>6.6215</v>
       </c>
       <c r="G20">
         <v>13.9</v>
@@ -2915,28 +2915,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M20">
-        <v>0.3155319</v>
+        <v>0.33306145</v>
       </c>
       <c r="N20">
-        <v>10.40079463061224</v>
+        <v>10.38326508061224</v>
       </c>
       <c r="O20">
-        <v>3.640278120714285</v>
+        <v>3.634142778214285</v>
       </c>
       <c r="P20">
-        <v>6.760516509897959</v>
+        <v>6.749122302397959</v>
       </c>
       <c r="Q20">
-        <v>6.860516509897959</v>
+        <v>6.849122302397959</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2514955015807386</v>
+        <v>0.2532571268890839</v>
       </c>
       <c r="T20">
-        <v>1.258008081720593</v>
+        <v>1.268781962810998</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>33.96273571899464</v>
+        <v>32.17522331273176</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2113503227801579</v>
+        <v>0.2105892342641102</v>
       </c>
       <c r="C21">
-        <v>28.45189104608361</v>
+        <v>28.16021409505597</v>
       </c>
       <c r="D21">
-        <v>21.17339104608362</v>
+        <v>21.23021409505597</v>
       </c>
       <c r="E21">
-        <v>-23.3785</v>
+        <v>-23.03</v>
       </c>
       <c r="F21">
-        <v>6.6215</v>
+        <v>6.970000000000001</v>
       </c>
       <c r="G21">
         <v>13.9</v>
@@ -2997,28 +2997,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M21">
-        <v>0.33306145</v>
+        <v>0.350591</v>
       </c>
       <c r="N21">
-        <v>10.38326508061224</v>
+        <v>10.36573553061224</v>
       </c>
       <c r="O21">
-        <v>3.634142778214285</v>
+        <v>3.628007435714285</v>
       </c>
       <c r="P21">
-        <v>6.749122302397959</v>
+        <v>6.737728094897959</v>
       </c>
       <c r="Q21">
-        <v>6.849122302397959</v>
+        <v>6.837728094897959</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2532571268890839</v>
+        <v>0.2550627928301378</v>
       </c>
       <c r="T21">
-        <v>1.268781962810998</v>
+        <v>1.279825190928662</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>32.17522331273176</v>
+        <v>30.56646214709517</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2105892342641102</v>
+        <v>0.2098281457480625</v>
       </c>
       <c r="C22">
-        <v>28.16021409505597</v>
+        <v>27.86884295687584</v>
       </c>
       <c r="D22">
-        <v>21.23021409505597</v>
+        <v>21.28734295687584</v>
       </c>
       <c r="E22">
-        <v>-23.03</v>
+        <v>-22.6815</v>
       </c>
       <c r="F22">
-        <v>6.970000000000001</v>
+        <v>7.318500000000001</v>
       </c>
       <c r="G22">
         <v>13.9</v>
@@ -3079,28 +3079,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M22">
-        <v>0.350591</v>
+        <v>0.36812055</v>
       </c>
       <c r="N22">
-        <v>10.36573553061224</v>
+        <v>10.34820598061224</v>
       </c>
       <c r="O22">
-        <v>3.628007435714285</v>
+        <v>3.621872093214285</v>
       </c>
       <c r="P22">
-        <v>6.737728094897959</v>
+        <v>6.726333887397959</v>
       </c>
       <c r="Q22">
-        <v>6.837728094897959</v>
+        <v>6.826333887397959</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2550627928301378</v>
+        <v>0.2569141718329905</v>
       </c>
       <c r="T22">
-        <v>1.279825190928662</v>
+        <v>1.291147994441709</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>30.56646214709517</v>
+        <v>29.11091633056683</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2098281457480625</v>
+        <v>0.2090670572320147</v>
       </c>
       <c r="C23">
-        <v>27.86884295687584</v>
+        <v>27.57778010696045</v>
       </c>
       <c r="D23">
-        <v>21.28734295687584</v>
+        <v>21.34478010696045</v>
       </c>
       <c r="E23">
-        <v>-22.6815</v>
+        <v>-22.333</v>
       </c>
       <c r="F23">
-        <v>7.3185</v>
+        <v>7.667000000000001</v>
       </c>
       <c r="G23">
         <v>13.9</v>
@@ -3161,28 +3161,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M23">
-        <v>0.36812055</v>
+        <v>0.3856501</v>
       </c>
       <c r="N23">
-        <v>10.34820598061224</v>
+        <v>10.33067643061224</v>
       </c>
       <c r="O23">
-        <v>3.621872093214285</v>
+        <v>3.615736750714285</v>
       </c>
       <c r="P23">
-        <v>6.726333887397959</v>
+        <v>6.714939679897959</v>
       </c>
       <c r="Q23">
-        <v>6.826333887397959</v>
+        <v>6.814939679897959</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2569141718329905</v>
+        <v>0.2588130220923266</v>
       </c>
       <c r="T23">
-        <v>1.291147994441709</v>
+        <v>1.302761126249963</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>29.11091633056683</v>
+        <v>27.78769286099562</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2090670572320147</v>
+        <v>0.208305968715967</v>
       </c>
       <c r="C24">
-        <v>27.57778010696045</v>
+        <v>27.28702804751581</v>
       </c>
       <c r="D24">
-        <v>21.34478010696045</v>
+        <v>21.40252804751581</v>
       </c>
       <c r="E24">
-        <v>-22.333</v>
+        <v>-21.9845</v>
       </c>
       <c r="F24">
-        <v>7.667000000000001</v>
+        <v>8.015500000000001</v>
       </c>
       <c r="G24">
         <v>13.9</v>
@@ -3243,28 +3243,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M24">
-        <v>0.3856501</v>
+        <v>0.4031796500000001</v>
       </c>
       <c r="N24">
-        <v>10.33067643061224</v>
+        <v>10.31314688061224</v>
       </c>
       <c r="O24">
-        <v>3.615736750714285</v>
+        <v>3.609601408214285</v>
       </c>
       <c r="P24">
-        <v>6.714939679897959</v>
+        <v>6.703545472397959</v>
       </c>
       <c r="Q24">
-        <v>6.814939679897959</v>
+        <v>6.803545472397959</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2588130220923266</v>
+        <v>0.2607611931376195</v>
       </c>
       <c r="T24">
-        <v>1.302761126249963</v>
+        <v>1.314675897845445</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>27.78769286099562</v>
+        <v>26.57953230182189</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.208305968715967</v>
+        <v>0.2075448801999193</v>
       </c>
       <c r="C25">
-        <v>27.28702804751581</v>
+        <v>26.9965893079001</v>
       </c>
       <c r="D25">
-        <v>21.40252804751581</v>
+        <v>21.4605893079001</v>
       </c>
       <c r="E25">
-        <v>-21.9845</v>
+        <v>-21.636</v>
       </c>
       <c r="F25">
-        <v>8.015500000000001</v>
+        <v>8.364000000000001</v>
       </c>
       <c r="G25">
         <v>13.9</v>
@@ -3325,28 +3325,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M25">
-        <v>0.4031796500000001</v>
+        <v>0.4207092</v>
       </c>
       <c r="N25">
-        <v>10.31314688061224</v>
+        <v>10.29561733061225</v>
       </c>
       <c r="O25">
-        <v>3.609601408214285</v>
+        <v>3.603466065714286</v>
       </c>
       <c r="P25">
-        <v>6.703545472397959</v>
+        <v>6.69215126489796</v>
       </c>
       <c r="Q25">
-        <v>6.803545472397959</v>
+        <v>6.792151264897959</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2607611931376195</v>
+        <v>0.262760631841999</v>
       </c>
       <c r="T25">
-        <v>1.314675897845445</v>
+        <v>1.32690421606186</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>26.57953230182189</v>
+        <v>25.47205178924598</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2075448801999193</v>
+        <v>0.2067837916838716</v>
       </c>
       <c r="C26">
-        <v>26.9965893079001</v>
+        <v>26.70646644499295</v>
       </c>
       <c r="D26">
-        <v>21.4605893079001</v>
+        <v>21.51896644499295</v>
       </c>
       <c r="E26">
-        <v>-21.636</v>
+        <v>-21.2875</v>
       </c>
       <c r="F26">
-        <v>8.364000000000001</v>
+        <v>8.7125</v>
       </c>
       <c r="G26">
         <v>13.9</v>
@@ -3407,28 +3407,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M26">
-        <v>0.4207092</v>
+        <v>0.43823875</v>
       </c>
       <c r="N26">
-        <v>10.29561733061225</v>
+        <v>10.27808778061224</v>
       </c>
       <c r="O26">
-        <v>3.603466065714286</v>
+        <v>3.597330723214285</v>
       </c>
       <c r="P26">
-        <v>6.69215126489796</v>
+        <v>6.680757057397959</v>
       </c>
       <c r="Q26">
-        <v>6.792151264897959</v>
+        <v>6.780757057397959</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.262760631841999</v>
+        <v>0.2648133889118288</v>
       </c>
       <c r="T26">
-        <v>1.32690421606186</v>
+        <v>1.339458622764047</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>25.47205178924598</v>
+        <v>24.45316971767614</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2067837916838716</v>
+        <v>0.2060227031678238</v>
       </c>
       <c r="C27">
-        <v>26.70646644499295</v>
+        <v>26.41666204357081</v>
       </c>
       <c r="D27">
-        <v>21.51896644499295</v>
+        <v>21.57766204357081</v>
       </c>
       <c r="E27">
-        <v>-21.2875</v>
+        <v>-20.939</v>
       </c>
       <c r="F27">
-        <v>8.7125</v>
+        <v>9.061</v>
       </c>
       <c r="G27">
         <v>13.9</v>
@@ -3489,28 +3489,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M27">
-        <v>0.43823875</v>
+        <v>0.4557683</v>
       </c>
       <c r="N27">
-        <v>10.27808778061224</v>
+        <v>10.26055823061224</v>
       </c>
       <c r="O27">
-        <v>3.597330723214285</v>
+        <v>3.591195380714285</v>
       </c>
       <c r="P27">
-        <v>6.680757057397959</v>
+        <v>6.669362849897959</v>
       </c>
       <c r="Q27">
-        <v>6.780757057397959</v>
+        <v>6.769362849897958</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2648133889118288</v>
+        <v>0.2669216259024647</v>
       </c>
       <c r="T27">
-        <v>1.339458622764047</v>
+        <v>1.352352337755482</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>24.45316971767614</v>
+        <v>23.51266319007321</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2060227031678238</v>
+        <v>0.2052616146517761</v>
       </c>
       <c r="C28">
-        <v>26.41666204357081</v>
+        <v>26.12717871668841</v>
       </c>
       <c r="D28">
-        <v>21.57766204357081</v>
+        <v>21.63667871668842</v>
       </c>
       <c r="E28">
-        <v>-20.939</v>
+        <v>-20.5905</v>
       </c>
       <c r="F28">
-        <v>9.061</v>
+        <v>9.409500000000001</v>
       </c>
       <c r="G28">
         <v>13.9</v>
@@ -3571,28 +3571,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M28">
-        <v>0.4557683</v>
+        <v>0.47329785</v>
       </c>
       <c r="N28">
-        <v>10.26055823061224</v>
+        <v>10.24302868061224</v>
       </c>
       <c r="O28">
-        <v>3.591195380714285</v>
+        <v>3.585060038214285</v>
       </c>
       <c r="P28">
-        <v>6.669362849897959</v>
+        <v>6.657968642397959</v>
       </c>
       <c r="Q28">
-        <v>6.769362849897958</v>
+        <v>6.757968642397959</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2669216259024647</v>
+        <v>0.2690876228106522</v>
       </c>
       <c r="T28">
-        <v>1.352352337755482</v>
+        <v>1.365599305212435</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>23.51266319007321</v>
+        <v>22.64182381266309</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2052616146517761</v>
+        <v>0.2045005261357284</v>
       </c>
       <c r="C29">
-        <v>26.12717871668841</v>
+        <v>25.83801910606658</v>
       </c>
       <c r="D29">
-        <v>21.63667871668842</v>
+        <v>21.69601910606658</v>
       </c>
       <c r="E29">
-        <v>-20.5905</v>
+        <v>-20.242</v>
       </c>
       <c r="F29">
-        <v>9.409500000000001</v>
+        <v>9.758000000000001</v>
       </c>
       <c r="G29">
         <v>13.9</v>
@@ -3653,28 +3653,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M29">
-        <v>0.47329785</v>
+        <v>0.4908274</v>
       </c>
       <c r="N29">
-        <v>10.24302868061224</v>
+        <v>10.22549913061224</v>
       </c>
       <c r="O29">
-        <v>3.585060038214285</v>
+        <v>3.578924695714285</v>
       </c>
       <c r="P29">
-        <v>6.657968642397959</v>
+        <v>6.646574434897959</v>
       </c>
       <c r="Q29">
-        <v>6.757968642397959</v>
+        <v>6.746574434897958</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2690876228106522</v>
+        <v>0.2713137862996227</v>
       </c>
       <c r="T29">
-        <v>1.365599305212435</v>
+        <v>1.379214243987637</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>22.64182381266309</v>
+        <v>21.83318724792512</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2045005261357284</v>
+        <v>0.2037394376196806</v>
       </c>
       <c r="C30">
-        <v>25.83801910606658</v>
+        <v>25.54918588248639</v>
       </c>
       <c r="D30">
-        <v>21.69601910606658</v>
+        <v>21.7556858824864</v>
       </c>
       <c r="E30">
-        <v>-20.242</v>
+        <v>-19.8935</v>
       </c>
       <c r="F30">
-        <v>9.758000000000001</v>
+        <v>10.1065</v>
       </c>
       <c r="G30">
         <v>13.9</v>
@@ -3735,28 +3735,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M30">
-        <v>0.4908274</v>
+        <v>0.5083569500000001</v>
       </c>
       <c r="N30">
-        <v>10.22549913061224</v>
+        <v>10.20796958061224</v>
       </c>
       <c r="O30">
-        <v>3.578924695714285</v>
+        <v>3.572789353214286</v>
       </c>
       <c r="P30">
-        <v>6.646574434897959</v>
+        <v>6.635180227397959</v>
       </c>
       <c r="Q30">
-        <v>6.746574434897958</v>
+        <v>6.735180227397959</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2713137862996227</v>
+        <v>0.2736026586192685</v>
       </c>
       <c r="T30">
-        <v>1.379214243987637</v>
+        <v>1.393212702164958</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>21.83318724792512</v>
+        <v>21.0803187221346</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2037394376196806</v>
+        <v>0.2029783491036329</v>
       </c>
       <c r="C31">
-        <v>25.54918588248639</v>
+        <v>25.26068174618987</v>
       </c>
       <c r="D31">
-        <v>21.7556858824864</v>
+        <v>21.81568174618987</v>
       </c>
       <c r="E31">
-        <v>-19.8935</v>
+        <v>-19.545</v>
       </c>
       <c r="F31">
-        <v>10.1065</v>
+        <v>10.455</v>
       </c>
       <c r="G31">
         <v>13.9</v>
@@ -3817,28 +3817,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M31">
-        <v>0.50835695</v>
+        <v>0.5258864999999999</v>
       </c>
       <c r="N31">
-        <v>10.20796958061224</v>
+        <v>10.19044003061224</v>
       </c>
       <c r="O31">
-        <v>3.572789353214286</v>
+        <v>3.566654010714285</v>
       </c>
       <c r="P31">
-        <v>6.635180227397959</v>
+        <v>6.623786019897959</v>
       </c>
       <c r="Q31">
-        <v>6.735180227397959</v>
+        <v>6.723786019897958</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2736026586192685</v>
+        <v>0.2759569272909042</v>
       </c>
       <c r="T31">
-        <v>1.393212702164958</v>
+        <v>1.407611116290202</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>21.0803187221346</v>
+        <v>20.37764143139679</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2029783491036329</v>
+        <v>0.2022172605875852</v>
       </c>
       <c r="C32">
-        <v>25.26068174618987</v>
+        <v>24.97250942728735</v>
       </c>
       <c r="D32">
-        <v>21.81568174618987</v>
+        <v>21.87600942728735</v>
       </c>
       <c r="E32">
-        <v>-19.545</v>
+        <v>-19.1965</v>
       </c>
       <c r="F32">
-        <v>10.455</v>
+        <v>10.8035</v>
       </c>
       <c r="G32">
         <v>13.9</v>
@@ -3899,28 +3899,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M32">
-        <v>0.5258864999999999</v>
+        <v>0.5434160499999999</v>
       </c>
       <c r="N32">
-        <v>10.19044003061224</v>
+        <v>10.17291048061225</v>
       </c>
       <c r="O32">
-        <v>3.566654010714285</v>
+        <v>3.560518668214285</v>
       </c>
       <c r="P32">
-        <v>6.623786019897959</v>
+        <v>6.612391812397959</v>
       </c>
       <c r="Q32">
-        <v>6.723786019897958</v>
+        <v>6.712391812397959</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2759569272909042</v>
+        <v>0.2783794356341814</v>
       </c>
       <c r="T32">
-        <v>1.407611116290202</v>
+        <v>1.42242687575241</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>20.37764143139679</v>
+        <v>19.72029815941625</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2022172605875852</v>
+        <v>0.2014561720715375</v>
       </c>
       <c r="C33">
-        <v>24.97250942728735</v>
+        <v>24.68467168617158</v>
       </c>
       <c r="D33">
-        <v>21.87600942728735</v>
+        <v>21.93667168617158</v>
       </c>
       <c r="E33">
-        <v>-19.1965</v>
+        <v>-18.848</v>
       </c>
       <c r="F33">
-        <v>10.8035</v>
+        <v>11.152</v>
       </c>
       <c r="G33">
         <v>13.9</v>
@@ -3981,28 +3981,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M33">
-        <v>0.5434160499999999</v>
+        <v>0.5609456</v>
       </c>
       <c r="N33">
-        <v>10.17291048061225</v>
+        <v>10.15538093061224</v>
       </c>
       <c r="O33">
-        <v>3.560518668214285</v>
+        <v>3.554383325714285</v>
       </c>
       <c r="P33">
-        <v>6.612391812397959</v>
+        <v>6.600997604897959</v>
       </c>
       <c r="Q33">
-        <v>6.712391812397959</v>
+        <v>6.700997604897958</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2783794356341814</v>
+        <v>0.2808731942228492</v>
       </c>
       <c r="T33">
-        <v>1.42242687575241</v>
+        <v>1.437678392845859</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>19.72029815941625</v>
+        <v>19.10403884193448</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2014561720715375</v>
+        <v>0.2006950835554897</v>
       </c>
       <c r="C34">
-        <v>24.68467168617158</v>
+        <v>24.39717131393878</v>
       </c>
       <c r="D34">
-        <v>21.93667168617158</v>
+        <v>21.99767131393879</v>
       </c>
       <c r="E34">
-        <v>-18.848</v>
+        <v>-18.4995</v>
       </c>
       <c r="F34">
-        <v>11.152</v>
+        <v>11.5005</v>
       </c>
       <c r="G34">
         <v>13.9</v>
@@ -4063,28 +4063,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M34">
-        <v>0.5609456</v>
+        <v>0.57847515</v>
       </c>
       <c r="N34">
-        <v>10.15538093061224</v>
+        <v>10.13785138061224</v>
       </c>
       <c r="O34">
-        <v>3.554383325714285</v>
+        <v>3.548247983214285</v>
       </c>
       <c r="P34">
-        <v>6.600997604897959</v>
+        <v>6.589603397397958</v>
       </c>
       <c r="Q34">
-        <v>6.700997604897958</v>
+        <v>6.689603397397958</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2808731942228492</v>
+        <v>0.2834413933664026</v>
       </c>
       <c r="T34">
-        <v>1.437678392845859</v>
+        <v>1.453385179106276</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>19.10403884193448</v>
+        <v>18.52512857399707</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2006950835554897</v>
+        <v>0.199933995039442</v>
       </c>
       <c r="C35">
-        <v>24.39717131393878</v>
+        <v>24.11001113281672</v>
       </c>
       <c r="D35">
-        <v>21.99767131393879</v>
+        <v>22.05901113281672</v>
       </c>
       <c r="E35">
-        <v>-18.4995</v>
+        <v>-18.151</v>
       </c>
       <c r="F35">
-        <v>11.5005</v>
+        <v>11.849</v>
       </c>
       <c r="G35">
         <v>13.9</v>
@@ -4145,28 +4145,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M35">
-        <v>0.57847515</v>
+        <v>0.5960047000000001</v>
       </c>
       <c r="N35">
-        <v>10.13785138061224</v>
+        <v>10.12032183061224</v>
       </c>
       <c r="O35">
-        <v>3.548247983214285</v>
+        <v>3.542112640714285</v>
       </c>
       <c r="P35">
-        <v>6.589603397397958</v>
+        <v>6.57820918989796</v>
       </c>
       <c r="Q35">
-        <v>6.689603397397958</v>
+        <v>6.678209189897959</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2834413933664026</v>
+        <v>0.2860874167264273</v>
       </c>
       <c r="T35">
-        <v>1.453385179106276</v>
+        <v>1.469567928586707</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>18.52512857399707</v>
+        <v>17.98027185123246</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.199933995039442</v>
+        <v>0.1991729065233943</v>
       </c>
       <c r="C36">
-        <v>24.11001113281672</v>
+        <v>23.82319399659994</v>
       </c>
       <c r="D36">
-        <v>22.05901113281672</v>
+        <v>22.12069399659994</v>
       </c>
       <c r="E36">
-        <v>-18.151</v>
+        <v>-17.8025</v>
       </c>
       <c r="F36">
-        <v>11.849</v>
+        <v>12.1975</v>
       </c>
       <c r="G36">
         <v>13.9</v>
@@ -4227,28 +4227,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M36">
-        <v>0.5960047000000001</v>
+        <v>0.6135342500000001</v>
       </c>
       <c r="N36">
-        <v>10.12032183061224</v>
+        <v>10.10279228061224</v>
       </c>
       <c r="O36">
-        <v>3.542112640714285</v>
+        <v>3.535977298214285</v>
       </c>
       <c r="P36">
-        <v>6.57820918989796</v>
+        <v>6.566814982397958</v>
       </c>
       <c r="Q36">
-        <v>6.678209189897959</v>
+        <v>6.666814982397958</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2860874167264273</v>
+        <v>0.2888148561898374</v>
       </c>
       <c r="T36">
-        <v>1.469567928586707</v>
+        <v>1.486248608820381</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>17.98027185123246</v>
+        <v>17.4665497983401</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1991729065233943</v>
+        <v>0.1984118180073466</v>
       </c>
       <c r="C37">
-        <v>23.82319399659994</v>
+        <v>23.53672279109237</v>
       </c>
       <c r="D37">
-        <v>22.12069399659994</v>
+        <v>22.18272279109237</v>
       </c>
       <c r="E37">
-        <v>-17.8025</v>
+        <v>-17.454</v>
       </c>
       <c r="F37">
-        <v>12.1975</v>
+        <v>12.546</v>
       </c>
       <c r="G37">
         <v>13.9</v>
@@ -4309,28 +4309,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M37">
-        <v>0.6135342500000001</v>
+        <v>0.6310638000000001</v>
       </c>
       <c r="N37">
-        <v>10.10279228061224</v>
+        <v>10.08526273061224</v>
       </c>
       <c r="O37">
-        <v>3.535977298214285</v>
+        <v>3.529841955714285</v>
       </c>
       <c r="P37">
-        <v>6.566814982397958</v>
+        <v>6.555420774897959</v>
       </c>
       <c r="Q37">
-        <v>6.666814982397958</v>
+        <v>6.655420774897959</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2888148561898374</v>
+        <v>0.291627528136479</v>
       </c>
       <c r="T37">
-        <v>1.486248608820381</v>
+        <v>1.503450560311358</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>17.4665497983401</v>
+        <v>16.98136785949732</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1984118180073466</v>
+        <v>0.1976507294912988</v>
       </c>
       <c r="C38">
-        <v>23.53672279109237</v>
+        <v>23.25060043455739</v>
       </c>
       <c r="D38">
-        <v>22.18272279109237</v>
+        <v>22.24510043455739</v>
       </c>
       <c r="E38">
-        <v>-17.454</v>
+        <v>-17.1055</v>
       </c>
       <c r="F38">
-        <v>12.546</v>
+        <v>12.8945</v>
       </c>
       <c r="G38">
         <v>13.9</v>
@@ -4391,28 +4391,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M38">
-        <v>0.6310638</v>
+        <v>0.64859335</v>
       </c>
       <c r="N38">
-        <v>10.08526273061224</v>
+        <v>10.06773318061224</v>
       </c>
       <c r="O38">
-        <v>3.529841955714285</v>
+        <v>3.523706613214285</v>
       </c>
       <c r="P38">
-        <v>6.555420774897959</v>
+        <v>6.544026567397959</v>
       </c>
       <c r="Q38">
-        <v>6.655420774897959</v>
+        <v>6.644026567397958</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.291627528136479</v>
+        <v>0.2945294912560299</v>
       </c>
       <c r="T38">
-        <v>1.503450560311358</v>
+        <v>1.52119860550046</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>16.98136785949732</v>
+        <v>16.5224119714028</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1976507294912988</v>
+        <v>0.1968896409752511</v>
       </c>
       <c r="C39">
-        <v>23.25060043455739</v>
+        <v>22.96482987817546</v>
       </c>
       <c r="D39">
-        <v>22.24510043455739</v>
+        <v>22.30782987817546</v>
       </c>
       <c r="E39">
-        <v>-17.1055</v>
+        <v>-16.757</v>
       </c>
       <c r="F39">
-        <v>12.8945</v>
+        <v>13.243</v>
       </c>
       <c r="G39">
         <v>13.9</v>
@@ -4473,28 +4473,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M39">
-        <v>0.64859335</v>
+        <v>0.6661229</v>
       </c>
       <c r="N39">
-        <v>10.06773318061224</v>
+        <v>10.05020363061224</v>
       </c>
       <c r="O39">
-        <v>3.523706613214285</v>
+        <v>3.517571270714285</v>
       </c>
       <c r="P39">
-        <v>6.544026567397959</v>
+        <v>6.53263235989796</v>
       </c>
       <c r="Q39">
-        <v>6.644026567397958</v>
+        <v>6.63263235989796</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2945294912560299</v>
+        <v>0.2975250660891147</v>
       </c>
       <c r="T39">
-        <v>1.52119860550046</v>
+        <v>1.539519168276309</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>16.5224119714028</v>
+        <v>16.08761165636588</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1968896409752511</v>
+        <v>0.1961285524592034</v>
       </c>
       <c r="C40">
-        <v>22.96482987817546</v>
+        <v>22.67941410650958</v>
       </c>
       <c r="D40">
-        <v>22.30782987817546</v>
+        <v>22.37091410650958</v>
       </c>
       <c r="E40">
-        <v>-16.757</v>
+        <v>-16.4085</v>
       </c>
       <c r="F40">
-        <v>13.243</v>
+        <v>13.5915</v>
       </c>
       <c r="G40">
         <v>13.9</v>
@@ -4555,28 +4555,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M40">
-        <v>0.6661229</v>
+        <v>0.6836524500000001</v>
       </c>
       <c r="N40">
-        <v>10.05020363061224</v>
+        <v>10.03267408061224</v>
       </c>
       <c r="O40">
-        <v>3.517571270714285</v>
+        <v>3.511435928214285</v>
       </c>
       <c r="P40">
-        <v>6.53263235989796</v>
+        <v>6.521238152397959</v>
       </c>
       <c r="Q40">
-        <v>6.63263235989796</v>
+        <v>6.621238152397959</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2975250660891147</v>
+        <v>0.3006188564904974</v>
       </c>
       <c r="T40">
-        <v>1.539519168276309</v>
+        <v>1.558440405241529</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>16.08761165636588</v>
+        <v>15.67510879338214</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1961285524592034</v>
+        <v>0.1953674639431557</v>
       </c>
       <c r="C41">
-        <v>22.67941410650958</v>
+        <v>22.39435613797862</v>
       </c>
       <c r="D41">
-        <v>22.37091410650958</v>
+        <v>22.43435613797862</v>
       </c>
       <c r="E41">
-        <v>-16.4085</v>
+        <v>-16.06</v>
       </c>
       <c r="F41">
-        <v>13.5915</v>
+        <v>13.94</v>
       </c>
       <c r="G41">
         <v>13.9</v>
@@ -4637,28 +4637,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M41">
-        <v>0.6836524500000001</v>
+        <v>0.7011820000000001</v>
       </c>
       <c r="N41">
-        <v>10.03267408061224</v>
+        <v>10.01514453061225</v>
       </c>
       <c r="O41">
-        <v>3.511435928214285</v>
+        <v>3.505300585714286</v>
       </c>
       <c r="P41">
-        <v>6.521238152397959</v>
+        <v>6.509843944897959</v>
       </c>
       <c r="Q41">
-        <v>6.621238152397959</v>
+        <v>6.609843944897959</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3006188564904974</v>
+        <v>0.3038157732385928</v>
       </c>
       <c r="T41">
-        <v>1.558440405241529</v>
+        <v>1.57799235010559</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>15.67510879338214</v>
+        <v>15.28323107354759</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1953674639431557</v>
+        <v>0.194606375427108</v>
       </c>
       <c r="C42">
-        <v>22.39435613797862</v>
+        <v>22.10965902533876</v>
       </c>
       <c r="D42">
-        <v>22.43435613797862</v>
+        <v>22.49815902533876</v>
       </c>
       <c r="E42">
-        <v>-16.06</v>
+        <v>-15.7115</v>
       </c>
       <c r="F42">
-        <v>13.94</v>
+        <v>14.2885</v>
       </c>
       <c r="G42">
         <v>13.9</v>
@@ -4719,28 +4719,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M42">
-        <v>0.7011820000000001</v>
+        <v>0.71871155</v>
       </c>
       <c r="N42">
-        <v>10.01514453061225</v>
+        <v>9.997614980612244</v>
       </c>
       <c r="O42">
-        <v>3.505300585714286</v>
+        <v>3.499165243214285</v>
       </c>
       <c r="P42">
-        <v>6.509843944897959</v>
+        <v>6.498449737397959</v>
       </c>
       <c r="Q42">
-        <v>6.609843944897959</v>
+        <v>6.598449737397958</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3038157732385928</v>
+        <v>0.3071210600459457</v>
       </c>
       <c r="T42">
-        <v>1.57799235010559</v>
+        <v>1.598207072761653</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.28323107354759</v>
+        <v>14.91046934004643</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.194606375427108</v>
+        <v>0.1938452869110602</v>
       </c>
       <c r="C43">
-        <v>22.10965902533876</v>
+        <v>21.82532585617315</v>
       </c>
       <c r="D43">
-        <v>22.49815902533876</v>
+        <v>22.56232585617315</v>
       </c>
       <c r="E43">
-        <v>-15.7115</v>
+        <v>-15.363</v>
       </c>
       <c r="F43">
-        <v>14.2885</v>
+        <v>14.637</v>
       </c>
       <c r="G43">
         <v>13.9</v>
@@ -4801,28 +4801,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M43">
-        <v>0.71871155</v>
+        <v>0.7362411000000001</v>
       </c>
       <c r="N43">
-        <v>9.997614980612244</v>
+        <v>9.980085430612244</v>
       </c>
       <c r="O43">
-        <v>3.499165243214285</v>
+        <v>3.493029900714285</v>
       </c>
       <c r="P43">
-        <v>6.498449737397959</v>
+        <v>6.487055529897958</v>
       </c>
       <c r="Q43">
-        <v>6.598449737397958</v>
+        <v>6.587055529897958</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3071210600459457</v>
+        <v>0.3105403222604486</v>
       </c>
       <c r="T43">
-        <v>1.598207072761653</v>
+        <v>1.619118854819649</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>14.91046934004643</v>
+        <v>14.55545816528341</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1938452869110602</v>
+        <v>0.1930841983950125</v>
       </c>
       <c r="C44">
-        <v>21.82532585617315</v>
+        <v>21.54135975338998</v>
       </c>
       <c r="D44">
-        <v>22.56232585617315</v>
+        <v>22.62685975338999</v>
       </c>
       <c r="E44">
-        <v>-15.363</v>
+        <v>-15.0145</v>
       </c>
       <c r="F44">
-        <v>14.637</v>
+        <v>14.9855</v>
       </c>
       <c r="G44">
         <v>13.9</v>
@@ -4883,28 +4883,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M44">
-        <v>0.7362411</v>
+        <v>0.75377065</v>
       </c>
       <c r="N44">
-        <v>9.980085430612245</v>
+        <v>9.962555880612245</v>
       </c>
       <c r="O44">
-        <v>3.493029900714286</v>
+        <v>3.486894558214285</v>
       </c>
       <c r="P44">
-        <v>6.48705552989796</v>
+        <v>6.47566132239796</v>
       </c>
       <c r="Q44">
-        <v>6.58705552989796</v>
+        <v>6.575661322397959</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3105403222604486</v>
+        <v>0.3140795585877412</v>
       </c>
       <c r="T44">
-        <v>1.619118854819649</v>
+        <v>1.640764383616522</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>14.55545816528342</v>
+        <v>14.2169591381838</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1930841983950125</v>
+        <v>0.1923231098789648</v>
       </c>
       <c r="C45">
-        <v>21.54135975338998</v>
+        <v>21.25776387572915</v>
       </c>
       <c r="D45">
-        <v>22.62685975338999</v>
+        <v>22.69176387572915</v>
       </c>
       <c r="E45">
-        <v>-15.0145</v>
+        <v>-14.666</v>
       </c>
       <c r="F45">
-        <v>14.9855</v>
+        <v>15.334</v>
       </c>
       <c r="G45">
         <v>13.9</v>
@@ -4965,28 +4965,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M45">
-        <v>0.75377065</v>
+        <v>0.7713002</v>
       </c>
       <c r="N45">
-        <v>9.962555880612245</v>
+        <v>9.945026330612244</v>
       </c>
       <c r="O45">
-        <v>3.486894558214285</v>
+        <v>3.480759215714285</v>
       </c>
       <c r="P45">
-        <v>6.47566132239796</v>
+        <v>6.464267114897959</v>
       </c>
       <c r="Q45">
-        <v>6.575661322397959</v>
+        <v>6.564267114897959</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3140795585877412</v>
+        <v>0.3177451962124371</v>
       </c>
       <c r="T45">
-        <v>1.640764383616522</v>
+        <v>1.663182967013283</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>14.2169591381838</v>
+        <v>13.89384643049781</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1923231098789648</v>
+        <v>0.1915620213629171</v>
       </c>
       <c r="C46">
-        <v>21.25776387572915</v>
+        <v>20.97454141827758</v>
       </c>
       <c r="D46">
-        <v>22.69176387572915</v>
+        <v>22.75704141827758</v>
       </c>
       <c r="E46">
-        <v>-14.666</v>
+        <v>-14.3175</v>
       </c>
       <c r="F46">
-        <v>15.334</v>
+        <v>15.6825</v>
       </c>
       <c r="G46">
         <v>13.9</v>
@@ -5047,28 +5047,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M46">
-        <v>0.7713002</v>
+        <v>0.78882975</v>
       </c>
       <c r="N46">
-        <v>9.945026330612244</v>
+        <v>9.927496780612245</v>
       </c>
       <c r="O46">
-        <v>3.480759215714285</v>
+        <v>3.474623873214286</v>
       </c>
       <c r="P46">
-        <v>6.464267114897959</v>
+        <v>6.452872907397959</v>
       </c>
       <c r="Q46">
-        <v>6.564267114897959</v>
+        <v>6.552872907397958</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3177451962124371</v>
+        <v>0.3215441297507582</v>
       </c>
       <c r="T46">
-        <v>1.663182967013283</v>
+        <v>1.686416771624472</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>13.89384643049781</v>
+        <v>13.58509428759786</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1915620213629171</v>
+        <v>0.1908009328468693</v>
       </c>
       <c r="C47">
-        <v>20.97454141827758</v>
+        <v>20.69169561299359</v>
       </c>
       <c r="D47">
-        <v>22.75704141827758</v>
+        <v>22.8226956129936</v>
       </c>
       <c r="E47">
-        <v>-14.3175</v>
+        <v>-13.969</v>
       </c>
       <c r="F47">
-        <v>15.6825</v>
+        <v>16.031</v>
       </c>
       <c r="G47">
         <v>13.9</v>
@@ -5129,28 +5129,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M47">
-        <v>0.78882975</v>
+        <v>0.8063593000000001</v>
       </c>
       <c r="N47">
-        <v>9.927496780612245</v>
+        <v>9.909967230612244</v>
       </c>
       <c r="O47">
-        <v>3.474623873214286</v>
+        <v>3.468488530714285</v>
       </c>
       <c r="P47">
-        <v>6.452872907397959</v>
+        <v>6.441478699897958</v>
       </c>
       <c r="Q47">
-        <v>6.552872907397958</v>
+        <v>6.541478699897958</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3215441297507582</v>
+        <v>0.3254837645312395</v>
       </c>
       <c r="T47">
-        <v>1.686416771624472</v>
+        <v>1.710511087517558</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>13.58509428759786</v>
+        <v>13.28976615091094</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1908009328468693</v>
+        <v>0.1900398443308216</v>
       </c>
       <c r="C48">
-        <v>20.69169561299359</v>
+        <v>20.40922972924031</v>
       </c>
       <c r="D48">
-        <v>22.8226956129936</v>
+        <v>22.88872972924031</v>
       </c>
       <c r="E48">
-        <v>-13.969</v>
+        <v>-13.6205</v>
       </c>
       <c r="F48">
-        <v>16.031</v>
+        <v>16.3795</v>
       </c>
       <c r="G48">
         <v>13.9</v>
@@ -5211,28 +5211,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M48">
-        <v>0.8063593000000001</v>
+        <v>0.82388885</v>
       </c>
       <c r="N48">
-        <v>9.909967230612244</v>
+        <v>9.892437680612245</v>
       </c>
       <c r="O48">
-        <v>3.468488530714285</v>
+        <v>3.462353188214286</v>
       </c>
       <c r="P48">
-        <v>6.441478699897958</v>
+        <v>6.43008449239796</v>
       </c>
       <c r="Q48">
-        <v>6.541478699897958</v>
+        <v>6.530084492397959</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3254837645312395</v>
+        <v>0.3295720647751351</v>
       </c>
       <c r="T48">
-        <v>1.710511087517558</v>
+        <v>1.735514622878306</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>13.28976615091094</v>
+        <v>13.00700516897667</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1900398443308216</v>
+        <v>0.1897467558147739</v>
       </c>
       <c r="C49">
-        <v>20.40922972924031</v>
+        <v>20.08626091107489</v>
       </c>
       <c r="D49">
-        <v>22.88872972924031</v>
+        <v>22.9142609110749</v>
       </c>
       <c r="E49">
-        <v>-13.6205</v>
+        <v>-13.272</v>
       </c>
       <c r="F49">
-        <v>16.3795</v>
+        <v>16.728</v>
       </c>
       <c r="G49">
         <v>13.9</v>
@@ -5293,45 +5293,45 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M49">
-        <v>0.82388885</v>
+        <v>0.8665104</v>
       </c>
       <c r="N49">
-        <v>9.892437680612245</v>
+        <v>9.849816130612245</v>
       </c>
       <c r="O49">
-        <v>3.462353188214286</v>
+        <v>3.447435645714286</v>
       </c>
       <c r="P49">
-        <v>6.43008449239796</v>
+        <v>6.402380484897959</v>
       </c>
       <c r="Q49">
-        <v>6.530084492397959</v>
+        <v>6.502380484897959</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3295720647751351</v>
+        <v>0.3338176073361036</v>
       </c>
       <c r="T49">
-        <v>1.735514622878306</v>
+        <v>1.761479832676007</v>
       </c>
       <c r="U49">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y49">
-        <v>13.00700516897667</v>
+        <v>12.36722205597561</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1897467558147739</v>
+        <v>0.1889954172987261</v>
       </c>
       <c r="C50">
-        <v>20.08626091107489</v>
+        <v>19.80347153104909</v>
       </c>
       <c r="D50">
-        <v>22.9142609110749</v>
+        <v>22.97997153104908</v>
       </c>
       <c r="E50">
-        <v>-13.272</v>
+        <v>-12.9235</v>
       </c>
       <c r="F50">
-        <v>16.728</v>
+        <v>17.0765</v>
       </c>
       <c r="G50">
         <v>13.9</v>
@@ -5375,28 +5375,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M50">
-        <v>0.8665104</v>
+        <v>0.8845626999999999</v>
       </c>
       <c r="N50">
-        <v>9.849816130612245</v>
+        <v>9.831763830612244</v>
       </c>
       <c r="O50">
-        <v>3.447435645714286</v>
+        <v>3.441117340714285</v>
       </c>
       <c r="P50">
-        <v>6.402380484897959</v>
+        <v>6.390646489897959</v>
       </c>
       <c r="Q50">
-        <v>6.502380484897959</v>
+        <v>6.490646489897959</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3338176073361036</v>
+        <v>0.3382296417622081</v>
       </c>
       <c r="T50">
-        <v>1.761479832676007</v>
+        <v>1.788463285995186</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>12.36722205597561</v>
+        <v>12.11482976911896</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1889954172987261</v>
+        <v>0.1882440787826784</v>
       </c>
       <c r="C51">
-        <v>19.80347153104909</v>
+        <v>19.52106010809471</v>
       </c>
       <c r="D51">
-        <v>22.97997153104908</v>
+        <v>23.04606010809471</v>
       </c>
       <c r="E51">
-        <v>-12.9235</v>
+        <v>-12.575</v>
       </c>
       <c r="F51">
-        <v>17.0765</v>
+        <v>17.425</v>
       </c>
       <c r="G51">
         <v>13.9</v>
@@ -5457,28 +5457,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M51">
-        <v>0.8845626999999999</v>
+        <v>0.9026150000000001</v>
       </c>
       <c r="N51">
-        <v>9.831763830612244</v>
+        <v>9.813711530612244</v>
       </c>
       <c r="O51">
-        <v>3.441117340714285</v>
+        <v>3.434799035714285</v>
       </c>
       <c r="P51">
-        <v>6.390646489897959</v>
+        <v>6.378912494897959</v>
       </c>
       <c r="Q51">
-        <v>6.490646489897959</v>
+        <v>6.478912494897958</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3382296417622081</v>
+        <v>0.3428181575653568</v>
       </c>
       <c r="T51">
-        <v>1.788463285995186</v>
+        <v>1.816526077447132</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>12.11482976911896</v>
+        <v>11.87253317373658</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1882440787826784</v>
+        <v>0.1874927402666307</v>
       </c>
       <c r="C52">
-        <v>19.52106010809471</v>
+        <v>19.23902991254075</v>
       </c>
       <c r="D52">
-        <v>23.04606010809471</v>
+        <v>23.11252991254075</v>
       </c>
       <c r="E52">
-        <v>-12.575</v>
+        <v>-12.2265</v>
       </c>
       <c r="F52">
-        <v>17.425</v>
+        <v>17.7735</v>
       </c>
       <c r="G52">
         <v>13.9</v>
@@ -5539,28 +5539,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M52">
-        <v>0.9026150000000001</v>
+        <v>0.9206673000000001</v>
       </c>
       <c r="N52">
-        <v>9.813711530612244</v>
+        <v>9.795659230612245</v>
       </c>
       <c r="O52">
-        <v>3.434799035714285</v>
+        <v>3.428480730714285</v>
       </c>
       <c r="P52">
-        <v>6.378912494897959</v>
+        <v>6.367178499897959</v>
       </c>
       <c r="Q52">
-        <v>6.478912494897958</v>
+        <v>6.467178499897958</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3428181575653568</v>
+        <v>0.3475939597278177</v>
       </c>
       <c r="T52">
-        <v>1.816526077447132</v>
+        <v>1.845734288958341</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>11.87253317373658</v>
+        <v>11.6397384056241</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1874927402666307</v>
+        <v>0.186741401750583</v>
       </c>
       <c r="C53">
-        <v>19.23902991254075</v>
+        <v>18.95738425255463</v>
       </c>
       <c r="D53">
-        <v>23.11252991254075</v>
+        <v>23.17938425255462</v>
       </c>
       <c r="E53">
-        <v>-12.2265</v>
+        <v>-11.878</v>
       </c>
       <c r="F53">
-        <v>17.7735</v>
+        <v>18.122</v>
       </c>
       <c r="G53">
         <v>13.9</v>
@@ -5621,28 +5621,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M53">
-        <v>0.9206673000000001</v>
+        <v>0.9387196</v>
       </c>
       <c r="N53">
-        <v>9.795659230612245</v>
+        <v>9.777606930612244</v>
       </c>
       <c r="O53">
-        <v>3.428480730714285</v>
+        <v>3.422162425714285</v>
       </c>
       <c r="P53">
-        <v>6.367178499897959</v>
+        <v>6.355444504897958</v>
       </c>
       <c r="Q53">
-        <v>6.467178499897958</v>
+        <v>6.455444504897958</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3475939597278177</v>
+        <v>0.3525687536470479</v>
       </c>
       <c r="T53">
-        <v>1.845734288958341</v>
+        <v>1.876159509282518</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>11.6397384056241</v>
+        <v>11.41589728243902</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.186741401750583</v>
+        <v>0.1859900632345352</v>
       </c>
       <c r="C54">
-        <v>18.95738425255463</v>
+        <v>18.67612647469108</v>
       </c>
       <c r="D54">
-        <v>23.17938425255462</v>
+        <v>23.24662647469108</v>
       </c>
       <c r="E54">
-        <v>-11.878</v>
+        <v>-11.5295</v>
       </c>
       <c r="F54">
-        <v>18.122</v>
+        <v>18.4705</v>
       </c>
       <c r="G54">
         <v>13.9</v>
@@ -5703,28 +5703,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M54">
-        <v>0.9387196</v>
+        <v>0.9567719</v>
       </c>
       <c r="N54">
-        <v>9.777606930612244</v>
+        <v>9.759554630612245</v>
       </c>
       <c r="O54">
-        <v>3.422162425714285</v>
+        <v>3.415844120714286</v>
       </c>
       <c r="P54">
-        <v>6.355444504897958</v>
+        <v>6.343710509897959</v>
       </c>
       <c r="Q54">
-        <v>6.455444504897958</v>
+        <v>6.443710509897959</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3525687536470479</v>
+        <v>0.3577552409245431</v>
       </c>
       <c r="T54">
-        <v>1.876159509282518</v>
+        <v>1.907879419833255</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.41589728243902</v>
+        <v>11.20050299409112</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1859900632345352</v>
+        <v>0.1852387247184875</v>
       </c>
       <c r="C55">
-        <v>18.67612647469108</v>
+        <v>18.39525996445058</v>
       </c>
       <c r="D55">
-        <v>23.24662647469108</v>
+        <v>23.31425996445059</v>
       </c>
       <c r="E55">
-        <v>-11.5295</v>
+        <v>-11.181</v>
       </c>
       <c r="F55">
-        <v>18.4705</v>
+        <v>18.819</v>
       </c>
       <c r="G55">
         <v>13.9</v>
@@ -5785,28 +5785,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M55">
-        <v>0.9567719</v>
+        <v>0.9748242000000001</v>
       </c>
       <c r="N55">
-        <v>9.759554630612245</v>
+        <v>9.741502330612244</v>
       </c>
       <c r="O55">
-        <v>3.415844120714286</v>
+        <v>3.409525815714285</v>
       </c>
       <c r="P55">
-        <v>6.343710509897959</v>
+        <v>6.331976514897958</v>
       </c>
       <c r="Q55">
-        <v>6.443710509897959</v>
+        <v>6.431976514897958</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3577552409245431</v>
+        <v>0.3631672276488859</v>
       </c>
       <c r="T55">
-        <v>1.907879419833255</v>
+        <v>1.940978456929676</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.20050299409112</v>
+        <v>10.99308627197831</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1852387247184875</v>
+        <v>0.1844873862024398</v>
       </c>
       <c r="C56">
-        <v>18.39525996445058</v>
+        <v>18.11478814684752</v>
       </c>
       <c r="D56">
-        <v>23.31425996445059</v>
+        <v>23.38228814684752</v>
       </c>
       <c r="E56">
-        <v>-11.181</v>
+        <v>-10.8325</v>
       </c>
       <c r="F56">
-        <v>18.819</v>
+        <v>19.1675</v>
       </c>
       <c r="G56">
         <v>13.9</v>
@@ -5867,28 +5867,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M56">
-        <v>0.9748242000000001</v>
+        <v>0.9928765000000002</v>
       </c>
       <c r="N56">
-        <v>9.741502330612244</v>
+        <v>9.723450030612245</v>
       </c>
       <c r="O56">
-        <v>3.409525815714285</v>
+        <v>3.403207510714286</v>
       </c>
       <c r="P56">
-        <v>6.331976514897958</v>
+        <v>6.32024251989796</v>
       </c>
       <c r="Q56">
-        <v>6.431976514897958</v>
+        <v>6.420242519897959</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3631672276488859</v>
+        <v>0.3688197471165329</v>
       </c>
       <c r="T56">
-        <v>1.940978456929676</v>
+        <v>1.975548562341494</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.99308627197831</v>
+        <v>10.79321197612416</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1844873862024398</v>
+        <v>0.1837360476863921</v>
       </c>
       <c r="C57">
-        <v>18.11478814684752</v>
+        <v>17.83471448698834</v>
       </c>
       <c r="D57">
-        <v>23.38228814684752</v>
+        <v>23.45071448698834</v>
       </c>
       <c r="E57">
-        <v>-10.8325</v>
+        <v>-10.484</v>
       </c>
       <c r="F57">
-        <v>19.1675</v>
+        <v>19.516</v>
       </c>
       <c r="G57">
         <v>13.9</v>
@@ -5949,28 +5949,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M57">
-        <v>0.9928765000000002</v>
+        <v>1.0109288</v>
       </c>
       <c r="N57">
-        <v>9.723450030612245</v>
+        <v>9.705397730612244</v>
       </c>
       <c r="O57">
-        <v>3.403207510714286</v>
+        <v>3.396889205714285</v>
       </c>
       <c r="P57">
-        <v>6.32024251989796</v>
+        <v>6.308508524897959</v>
       </c>
       <c r="Q57">
-        <v>6.420242519897959</v>
+        <v>6.408508524897958</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3688197471165329</v>
+        <v>0.3747291992872547</v>
       </c>
       <c r="T57">
-        <v>1.975548562341494</v>
+        <v>2.011690036181122</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.79321197612416</v>
+        <v>10.60047604797909</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1837360476863921</v>
+        <v>0.1829847091703443</v>
       </c>
       <c r="C58">
-        <v>17.83471448698834</v>
+        <v>17.55504249065998</v>
       </c>
       <c r="D58">
-        <v>23.45071448698834</v>
+        <v>23.51954249065998</v>
       </c>
       <c r="E58">
-        <v>-10.484</v>
+        <v>-10.1355</v>
       </c>
       <c r="F58">
-        <v>19.516</v>
+        <v>19.8645</v>
       </c>
       <c r="G58">
         <v>13.9</v>
@@ -6031,28 +6031,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M58">
-        <v>1.0109288</v>
+        <v>1.0289811</v>
       </c>
       <c r="N58">
-        <v>9.705397730612244</v>
+        <v>9.687345430612243</v>
       </c>
       <c r="O58">
-        <v>3.396889205714285</v>
+        <v>3.390570900714285</v>
       </c>
       <c r="P58">
-        <v>6.308508524897959</v>
+        <v>6.296774529897958</v>
       </c>
       <c r="Q58">
-        <v>6.408508524897958</v>
+        <v>6.396774529897958</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3747291992872547</v>
+        <v>0.3809135096984752</v>
       </c>
       <c r="T58">
-        <v>2.011690036181122</v>
+        <v>2.049512508803988</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>10.60047604797909</v>
+        <v>10.41450278397945</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1829847091703443</v>
+        <v>0.1822333706542966</v>
       </c>
       <c r="C59">
-        <v>17.55504249065998</v>
+        <v>17.27577570492852</v>
       </c>
       <c r="D59">
-        <v>23.51954249065998</v>
+        <v>23.58877570492853</v>
       </c>
       <c r="E59">
-        <v>-10.1355</v>
+        <v>-9.786999999999995</v>
       </c>
       <c r="F59">
-        <v>19.8645</v>
+        <v>20.213</v>
       </c>
       <c r="G59">
         <v>13.9</v>
@@ -6113,28 +6113,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M59">
-        <v>1.0289811</v>
+        <v>1.0470334</v>
       </c>
       <c r="N59">
-        <v>9.687345430612243</v>
+        <v>9.669293130612244</v>
       </c>
       <c r="O59">
-        <v>3.390570900714285</v>
+        <v>3.384252595714285</v>
       </c>
       <c r="P59">
-        <v>6.296774529897958</v>
+        <v>6.285040534897959</v>
       </c>
       <c r="Q59">
-        <v>6.396774529897958</v>
+        <v>6.385040534897959</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3809135096984752</v>
+        <v>0.3873923110816587</v>
       </c>
       <c r="T59">
-        <v>2.049512508803988</v>
+        <v>2.089136051551753</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.41450278397945</v>
+        <v>10.23494239115222</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1822333706542966</v>
+        <v>0.1814820321382488</v>
       </c>
       <c r="C60">
-        <v>17.27577570492853</v>
+        <v>16.99691771874864</v>
       </c>
       <c r="D60">
-        <v>23.58877570492853</v>
+        <v>23.65841771874864</v>
       </c>
       <c r="E60">
-        <v>-9.786999999999999</v>
+        <v>-9.438500000000001</v>
       </c>
       <c r="F60">
-        <v>20.213</v>
+        <v>20.5615</v>
       </c>
       <c r="G60">
         <v>13.9</v>
@@ -6195,28 +6195,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M60">
-        <v>1.0470334</v>
+        <v>1.0650857</v>
       </c>
       <c r="N60">
-        <v>9.669293130612244</v>
+        <v>9.651240830612245</v>
       </c>
       <c r="O60">
-        <v>3.384252595714285</v>
+        <v>3.377934290714286</v>
       </c>
       <c r="P60">
-        <v>6.285040534897959</v>
+        <v>6.273306539897959</v>
       </c>
       <c r="Q60">
-        <v>6.385040534897959</v>
+        <v>6.373306539897959</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3873923110816585</v>
+        <v>0.3941871515567045</v>
       </c>
       <c r="T60">
-        <v>2.089136051551752</v>
+        <v>2.13069245004331</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.23494239115222</v>
+        <v>10.06146879130219</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1814820321382488</v>
+        <v>0.1807306936222011</v>
       </c>
       <c r="C61">
-        <v>16.99691771874864</v>
+        <v>16.71847216358364</v>
       </c>
       <c r="D61">
-        <v>23.65841771874864</v>
+        <v>23.72847216358364</v>
       </c>
       <c r="E61">
-        <v>-9.438500000000001</v>
+        <v>-9.09</v>
       </c>
       <c r="F61">
-        <v>20.5615</v>
+        <v>20.91</v>
       </c>
       <c r="G61">
         <v>13.9</v>
@@ -6277,28 +6277,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M61">
-        <v>1.0650857</v>
+        <v>1.083138</v>
       </c>
       <c r="N61">
-        <v>9.651240830612245</v>
+        <v>9.633188530612244</v>
       </c>
       <c r="O61">
-        <v>3.377934290714286</v>
+        <v>3.371615985714286</v>
       </c>
       <c r="P61">
-        <v>6.273306539897959</v>
+        <v>6.261572544897959</v>
       </c>
       <c r="Q61">
-        <v>6.373306539897959</v>
+        <v>6.361572544897959</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3941871515567045</v>
+        <v>0.4013217340555029</v>
       </c>
       <c r="T61">
-        <v>2.13069245004331</v>
+        <v>2.174326668459446</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.06146879130219</v>
+        <v>9.893777644780485</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1807306936222011</v>
+        <v>0.1806534051061534</v>
       </c>
       <c r="C62">
-        <v>16.71847216358364</v>
+        <v>16.37720204872731</v>
       </c>
       <c r="D62">
-        <v>23.72847216358364</v>
+        <v>23.73570204872731</v>
       </c>
       <c r="E62">
-        <v>-9.09</v>
+        <v>-8.741499999999998</v>
       </c>
       <c r="F62">
-        <v>20.91</v>
+        <v>21.2585</v>
       </c>
       <c r="G62">
         <v>13.9</v>
@@ -6359,45 +6359,45 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M62">
-        <v>1.083138</v>
+        <v>1.13732975</v>
       </c>
       <c r="N62">
-        <v>9.633188530612244</v>
+        <v>9.578996780612243</v>
       </c>
       <c r="O62">
-        <v>3.371615985714286</v>
+        <v>3.352648873214285</v>
       </c>
       <c r="P62">
-        <v>6.261572544897959</v>
+        <v>6.226347907397958</v>
       </c>
       <c r="Q62">
-        <v>6.361572544897959</v>
+        <v>6.326347907397958</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4013217340555029</v>
+        <v>0.4088221925798806</v>
       </c>
       <c r="T62">
-        <v>2.174326668459446</v>
+        <v>2.22019853910205</v>
       </c>
       <c r="U62">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V62">
         <v>0.35</v>
       </c>
       <c r="W62">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>9.893777644780485</v>
+        <v>9.422356647763976</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1806534051061534</v>
+        <v>0.1799131165901057</v>
       </c>
       <c r="C63">
-        <v>16.37720204872731</v>
+        <v>16.09817552876935</v>
       </c>
       <c r="D63">
-        <v>23.73570204872731</v>
+        <v>23.80517552876935</v>
       </c>
       <c r="E63">
-        <v>-8.741499999999998</v>
+        <v>-8.393000000000001</v>
       </c>
       <c r="F63">
-        <v>21.2585</v>
+        <v>21.607</v>
       </c>
       <c r="G63">
         <v>13.9</v>
@@ -6441,28 +6441,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M63">
-        <v>1.13732975</v>
+        <v>1.1559745</v>
       </c>
       <c r="N63">
-        <v>9.578996780612243</v>
+        <v>9.560352030612245</v>
       </c>
       <c r="O63">
-        <v>3.352648873214285</v>
+        <v>3.346123210714286</v>
       </c>
       <c r="P63">
-        <v>6.226347907397958</v>
+        <v>6.21422881989796</v>
       </c>
       <c r="Q63">
-        <v>6.326347907397958</v>
+        <v>6.314228819897959</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4088221925798806</v>
+        <v>0.4167174120792256</v>
       </c>
       <c r="T63">
-        <v>2.22019853910205</v>
+        <v>2.268484718725845</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>9.422356647763976</v>
+        <v>9.270383153445206</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1799131165901057</v>
+        <v>0.1791728280740579</v>
       </c>
       <c r="C64">
-        <v>16.09817552876935</v>
+        <v>15.81955689504601</v>
       </c>
       <c r="D64">
-        <v>23.80517552876935</v>
+        <v>23.87505689504601</v>
       </c>
       <c r="E64">
-        <v>-8.393000000000001</v>
+        <v>-8.044499999999999</v>
       </c>
       <c r="F64">
-        <v>21.607</v>
+        <v>21.9555</v>
       </c>
       <c r="G64">
         <v>13.9</v>
@@ -6523,28 +6523,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M64">
-        <v>1.1559745</v>
+        <v>1.17461925</v>
       </c>
       <c r="N64">
-        <v>9.560352030612245</v>
+        <v>9.541707280612243</v>
       </c>
       <c r="O64">
-        <v>3.346123210714286</v>
+        <v>3.339597548214285</v>
       </c>
       <c r="P64">
-        <v>6.21422881989796</v>
+        <v>6.202109732397958</v>
       </c>
       <c r="Q64">
-        <v>6.314228819897959</v>
+        <v>6.302109732397958</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4167174120792256</v>
+        <v>0.4250394002001566</v>
       </c>
       <c r="T64">
-        <v>2.268484718725845</v>
+        <v>2.319380962113087</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.270383153445206</v>
+        <v>9.123234214501629</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1791728280740579</v>
+        <v>0.1784325395580103</v>
       </c>
       <c r="C65">
-        <v>15.81955689504601</v>
+        <v>15.54134975024875</v>
       </c>
       <c r="D65">
-        <v>23.87505689504601</v>
+        <v>23.94534975024875</v>
       </c>
       <c r="E65">
-        <v>-8.044499999999999</v>
+        <v>-7.695999999999998</v>
       </c>
       <c r="F65">
-        <v>21.9555</v>
+        <v>22.304</v>
       </c>
       <c r="G65">
         <v>13.9</v>
@@ -6605,28 +6605,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M65">
-        <v>1.17461925</v>
+        <v>1.193264</v>
       </c>
       <c r="N65">
-        <v>9.541707280612243</v>
+        <v>9.523062530612243</v>
       </c>
       <c r="O65">
-        <v>3.339597548214285</v>
+        <v>3.333071885714285</v>
       </c>
       <c r="P65">
-        <v>6.202109732397958</v>
+        <v>6.189990644897959</v>
       </c>
       <c r="Q65">
-        <v>6.302109732397958</v>
+        <v>6.289990644897959</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4250394002001566</v>
+        <v>0.4338237209944729</v>
       </c>
       <c r="T65">
-        <v>2.319380962113087</v>
+        <v>2.373104774577399</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.123234214501629</v>
+        <v>8.980683679900041</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1784325395580103</v>
+        <v>0.1776922510419625</v>
       </c>
       <c r="C66">
-        <v>15.54134975024875</v>
+        <v>15.26355773962247</v>
       </c>
       <c r="D66">
-        <v>23.94534975024875</v>
+        <v>24.01605773962247</v>
       </c>
       <c r="E66">
-        <v>-7.695999999999998</v>
+        <v>-7.347499999999997</v>
       </c>
       <c r="F66">
-        <v>22.304</v>
+        <v>22.6525</v>
       </c>
       <c r="G66">
         <v>13.9</v>
@@ -6687,28 +6687,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M66">
-        <v>1.193264</v>
+        <v>1.21190875</v>
       </c>
       <c r="N66">
-        <v>9.523062530612243</v>
+        <v>9.504417780612243</v>
       </c>
       <c r="O66">
-        <v>3.333071885714285</v>
+        <v>3.326546223214285</v>
       </c>
       <c r="P66">
-        <v>6.189990644897959</v>
+        <v>6.177871557397959</v>
       </c>
       <c r="Q66">
-        <v>6.289990644897959</v>
+        <v>6.277871557397958</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4338237209944729</v>
+        <v>0.4431100029770358</v>
       </c>
       <c r="T66">
-        <v>2.373104774577399</v>
+        <v>2.429898519182528</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.980683679900041</v>
+        <v>8.842519315593886</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1776922510419625</v>
+        <v>0.1769519625259148</v>
       </c>
       <c r="C67">
-        <v>15.26355773962247</v>
+        <v>14.98618455159562</v>
       </c>
       <c r="D67">
-        <v>24.01605773962247</v>
+        <v>24.08718455159562</v>
       </c>
       <c r="E67">
-        <v>-7.347499999999997</v>
+        <v>-6.998999999999999</v>
       </c>
       <c r="F67">
-        <v>22.6525</v>
+        <v>23.001</v>
       </c>
       <c r="G67">
         <v>13.9</v>
@@ -6769,28 +6769,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M67">
-        <v>1.21190875</v>
+        <v>1.2305535</v>
       </c>
       <c r="N67">
-        <v>9.504417780612243</v>
+        <v>9.485773030612243</v>
       </c>
       <c r="O67">
-        <v>3.326546223214285</v>
+        <v>3.320020560714285</v>
       </c>
       <c r="P67">
-        <v>6.177871557397959</v>
+        <v>6.165752469897958</v>
       </c>
       <c r="Q67">
-        <v>6.277871557397958</v>
+        <v>6.265752469897958</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4431100029770358</v>
+        <v>0.4529425368409258</v>
       </c>
       <c r="T67">
-        <v>2.429898519182528</v>
+        <v>2.490033072293841</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.842519315593886</v>
+        <v>8.7085417502061</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1769519625259148</v>
+        <v>0.1762116740098671</v>
       </c>
       <c r="C68">
-        <v>14.98618455159562</v>
+        <v>14.70923391842154</v>
       </c>
       <c r="D68">
-        <v>24.08718455159562</v>
+        <v>24.15873391842154</v>
       </c>
       <c r="E68">
-        <v>-6.998999999999999</v>
+        <v>-6.650499999999997</v>
       </c>
       <c r="F68">
-        <v>23.001</v>
+        <v>23.3495</v>
       </c>
       <c r="G68">
         <v>13.9</v>
@@ -6851,28 +6851,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M68">
-        <v>1.2305535</v>
+        <v>1.24919825</v>
       </c>
       <c r="N68">
-        <v>9.485773030612243</v>
+        <v>9.467128280612243</v>
       </c>
       <c r="O68">
-        <v>3.320020560714285</v>
+        <v>3.313494898214285</v>
       </c>
       <c r="P68">
-        <v>6.165752469897958</v>
+        <v>6.153633382397958</v>
       </c>
       <c r="Q68">
-        <v>6.265752469897958</v>
+        <v>6.253633382397958</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4529425368409258</v>
+        <v>0.4633709818480821</v>
       </c>
       <c r="T68">
-        <v>2.490033072293841</v>
+        <v>2.553812143775537</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.7085417502061</v>
+        <v>8.578563515128398</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1762116740098671</v>
+        <v>0.1754713854938193</v>
       </c>
       <c r="C69">
-        <v>14.70923391842154</v>
+        <v>14.43270961683135</v>
       </c>
       <c r="D69">
-        <v>24.15873391842154</v>
+        <v>24.23070961683135</v>
       </c>
       <c r="E69">
-        <v>-6.650499999999997</v>
+        <v>-6.301999999999996</v>
       </c>
       <c r="F69">
-        <v>23.3495</v>
+        <v>23.698</v>
       </c>
       <c r="G69">
         <v>13.9</v>
@@ -6933,28 +6933,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M69">
-        <v>1.24919825</v>
+        <v>1.267843</v>
       </c>
       <c r="N69">
-        <v>9.467128280612243</v>
+        <v>9.448483530612243</v>
       </c>
       <c r="O69">
-        <v>3.313494898214285</v>
+        <v>3.306969235714285</v>
       </c>
       <c r="P69">
-        <v>6.153633382397958</v>
+        <v>6.141514294897958</v>
       </c>
       <c r="Q69">
-        <v>6.253633382397958</v>
+        <v>6.241514294897958</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4633709818480821</v>
+        <v>0.4744512046681855</v>
       </c>
       <c r="T69">
-        <v>2.553812143775537</v>
+        <v>2.621577407224839</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.578563515128398</v>
+        <v>8.452408169317685</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1754713854938193</v>
+        <v>0.1747310969777716</v>
       </c>
       <c r="C70">
-        <v>14.43270961683135</v>
+        <v>14.15661546869845</v>
       </c>
       <c r="D70">
-        <v>24.23070961683135</v>
+        <v>24.30311546869845</v>
       </c>
       <c r="E70">
-        <v>-6.301999999999996</v>
+        <v>-5.953499999999998</v>
       </c>
       <c r="F70">
-        <v>23.698</v>
+        <v>24.0465</v>
       </c>
       <c r="G70">
         <v>13.9</v>
@@ -7015,28 +7015,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M70">
-        <v>1.267843</v>
+        <v>1.28648775</v>
       </c>
       <c r="N70">
-        <v>9.448483530612243</v>
+        <v>9.429838780612243</v>
       </c>
       <c r="O70">
-        <v>3.306969235714285</v>
+        <v>3.300443573214285</v>
       </c>
       <c r="P70">
-        <v>6.141514294897958</v>
+        <v>6.129395207397959</v>
       </c>
       <c r="Q70">
-        <v>6.241514294897958</v>
+        <v>6.229395207397959</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4744512046681855</v>
+        <v>0.4862462805734569</v>
       </c>
       <c r="T70">
-        <v>2.621577407224839</v>
+        <v>2.693714623154741</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.452408169317685</v>
+        <v>8.329909500197139</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1747310969777716</v>
+        <v>0.1739908084617239</v>
       </c>
       <c r="C71">
-        <v>14.15661546869845</v>
+        <v>13.88095534171501</v>
       </c>
       <c r="D71">
-        <v>24.30311546869845</v>
+        <v>24.37595534171501</v>
       </c>
       <c r="E71">
-        <v>-5.953499999999998</v>
+        <v>-5.604999999999997</v>
       </c>
       <c r="F71">
-        <v>24.0465</v>
+        <v>24.395</v>
       </c>
       <c r="G71">
         <v>13.9</v>
@@ -7097,28 +7097,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M71">
-        <v>1.28648775</v>
+        <v>1.3051325</v>
       </c>
       <c r="N71">
-        <v>9.429838780612243</v>
+        <v>9.411194030612243</v>
       </c>
       <c r="O71">
-        <v>3.300443573214285</v>
+        <v>3.293917910714285</v>
       </c>
       <c r="P71">
-        <v>6.129395207397959</v>
+        <v>6.117276119897959</v>
       </c>
       <c r="Q71">
-        <v>6.229395207397959</v>
+        <v>6.217276119897958</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4862462805734569</v>
+        <v>0.498827694872413</v>
       </c>
       <c r="T71">
-        <v>2.693714623154741</v>
+        <v>2.770660986813303</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.329909500197139</v>
+        <v>8.210910793051465</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1739908084617239</v>
+        <v>0.1732505199456762</v>
       </c>
       <c r="C72">
-        <v>13.88095534171501</v>
+        <v>13.60573315008068</v>
       </c>
       <c r="D72">
-        <v>24.37595534171501</v>
+        <v>24.44923315008069</v>
       </c>
       <c r="E72">
-        <v>-5.604999999999997</v>
+        <v>-5.256499999999996</v>
       </c>
       <c r="F72">
-        <v>24.395</v>
+        <v>24.7435</v>
       </c>
       <c r="G72">
         <v>13.9</v>
@@ -7179,28 +7179,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M72">
-        <v>1.3051325</v>
+        <v>1.32377725</v>
       </c>
       <c r="N72">
-        <v>9.411194030612243</v>
+        <v>9.392549280612243</v>
       </c>
       <c r="O72">
-        <v>3.293917910714285</v>
+        <v>3.287392248214285</v>
       </c>
       <c r="P72">
-        <v>6.117276119897959</v>
+        <v>6.105157032397958</v>
       </c>
       <c r="Q72">
-        <v>6.217276119897958</v>
+        <v>6.205157032397958</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.498827694872413</v>
+        <v>0.5122767929161248</v>
       </c>
       <c r="T72">
-        <v>2.770660986813303</v>
+        <v>2.852913996241422</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.210910793051465</v>
+        <v>8.095264162163417</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1732505199456761</v>
+        <v>0.1725102314296284</v>
       </c>
       <c r="C73">
-        <v>13.60573315008069</v>
+        <v>13.33095285520376</v>
       </c>
       <c r="D73">
-        <v>24.44923315008069</v>
+        <v>24.52295285520376</v>
       </c>
       <c r="E73">
-        <v>-5.256499999999999</v>
+        <v>-4.908000000000001</v>
       </c>
       <c r="F73">
-        <v>24.7435</v>
+        <v>25.092</v>
       </c>
       <c r="G73">
         <v>13.9</v>
@@ -7261,28 +7261,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M73">
-        <v>1.32377725</v>
+        <v>1.342422</v>
       </c>
       <c r="N73">
-        <v>9.392549280612243</v>
+        <v>9.373904530612243</v>
       </c>
       <c r="O73">
-        <v>3.287392248214285</v>
+        <v>3.280866585714285</v>
       </c>
       <c r="P73">
-        <v>6.105157032397958</v>
+        <v>6.093037944897958</v>
       </c>
       <c r="Q73">
-        <v>6.205157032397958</v>
+        <v>6.193037944897958</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5122767929161246</v>
+        <v>0.5266865408201014</v>
       </c>
       <c r="T73">
-        <v>2.852913996241421</v>
+        <v>2.94104222062869</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.095264162163417</v>
+        <v>7.982829937688926</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1725102314296284</v>
+        <v>0.1717699429135807</v>
       </c>
       <c r="C74">
-        <v>13.33095285520376</v>
+        <v>13.05661846641497</v>
       </c>
       <c r="D74">
-        <v>24.52295285520376</v>
+        <v>24.59711846641497</v>
       </c>
       <c r="E74">
-        <v>-4.908000000000001</v>
+        <v>-4.5595</v>
       </c>
       <c r="F74">
-        <v>25.092</v>
+        <v>25.4405</v>
       </c>
       <c r="G74">
         <v>13.9</v>
@@ -7343,28 +7343,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M74">
-        <v>1.342422</v>
+        <v>1.36106675</v>
       </c>
       <c r="N74">
-        <v>9.373904530612243</v>
+        <v>9.355259780612244</v>
       </c>
       <c r="O74">
-        <v>3.280866585714285</v>
+        <v>3.274340923214285</v>
       </c>
       <c r="P74">
-        <v>6.093037944897958</v>
+        <v>6.080918857397958</v>
       </c>
       <c r="Q74">
-        <v>6.193037944897958</v>
+        <v>6.180918857397958</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5266865408201014</v>
+        <v>0.5421636774577062</v>
       </c>
       <c r="T74">
-        <v>2.94104222062869</v>
+        <v>3.035698461637239</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.982829937688926</v>
+        <v>7.873476102926064</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1717699429135807</v>
+        <v>0.171029654397533</v>
       </c>
       <c r="C75">
-        <v>13.05661846641497</v>
+        <v>12.78273404169445</v>
       </c>
       <c r="D75">
-        <v>24.59711846641497</v>
+        <v>24.67173404169445</v>
       </c>
       <c r="E75">
-        <v>-4.5595</v>
+        <v>-4.210999999999999</v>
       </c>
       <c r="F75">
-        <v>25.4405</v>
+        <v>25.789</v>
       </c>
       <c r="G75">
         <v>13.9</v>
@@ -7425,28 +7425,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M75">
-        <v>1.36106675</v>
+        <v>1.3797115</v>
       </c>
       <c r="N75">
-        <v>9.355259780612244</v>
+        <v>9.336615030612244</v>
       </c>
       <c r="O75">
-        <v>3.274340923214285</v>
+        <v>3.267815260714285</v>
       </c>
       <c r="P75">
-        <v>6.080918857397958</v>
+        <v>6.068799769897959</v>
       </c>
       <c r="Q75">
-        <v>6.180918857397958</v>
+        <v>6.168799769897959</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5421636774577062</v>
+        <v>0.5588313630674344</v>
       </c>
       <c r="T75">
-        <v>3.035698461637239</v>
+        <v>3.137635951954137</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.873476102926064</v>
+        <v>7.767077777210847</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.171029654397533</v>
+        <v>0.1702893658814852</v>
       </c>
       <c r="C76">
-        <v>12.78273404169445</v>
+        <v>12.50930368841183</v>
       </c>
       <c r="D76">
-        <v>24.67173404169445</v>
+        <v>24.74680368841183</v>
       </c>
       <c r="E76">
-        <v>-4.210999999999999</v>
+        <v>-3.862499999999997</v>
       </c>
       <c r="F76">
-        <v>25.789</v>
+        <v>26.1375</v>
       </c>
       <c r="G76">
         <v>13.9</v>
@@ -7507,28 +7507,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M76">
-        <v>1.3797115</v>
+        <v>1.39835625</v>
       </c>
       <c r="N76">
-        <v>9.336615030612244</v>
+        <v>9.317970280612244</v>
       </c>
       <c r="O76">
-        <v>3.267815260714285</v>
+        <v>3.261289598214285</v>
       </c>
       <c r="P76">
-        <v>6.068799769897959</v>
+        <v>6.056680682397959</v>
       </c>
       <c r="Q76">
-        <v>6.168799769897959</v>
+        <v>6.156680682397958</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5588313630674344</v>
+        <v>0.576832463525941</v>
       </c>
       <c r="T76">
-        <v>3.137635951954137</v>
+        <v>3.247728441496388</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.767077777210847</v>
+        <v>7.663516740181368</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1702893658814852</v>
+        <v>0.1699442773654375</v>
       </c>
       <c r="C77">
-        <v>12.50930368841183</v>
+        <v>12.19595404533254</v>
       </c>
       <c r="D77">
-        <v>24.74680368841183</v>
+        <v>24.78195404533254</v>
       </c>
       <c r="E77">
-        <v>-3.862499999999997</v>
+        <v>-3.513999999999999</v>
       </c>
       <c r="F77">
-        <v>26.1375</v>
+        <v>26.486</v>
       </c>
       <c r="G77">
         <v>13.9</v>
@@ -7589,45 +7589,45 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M77">
-        <v>1.39835625</v>
+        <v>1.4381898</v>
       </c>
       <c r="N77">
-        <v>9.317970280612244</v>
+        <v>9.278136730612244</v>
       </c>
       <c r="O77">
-        <v>3.261289598214285</v>
+        <v>3.247347855714285</v>
       </c>
       <c r="P77">
-        <v>6.056680682397959</v>
+        <v>6.03078887489796</v>
       </c>
       <c r="Q77">
-        <v>6.156680682397958</v>
+        <v>6.130788874897959</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.576832463525941</v>
+        <v>0.596333655689323</v>
       </c>
       <c r="T77">
-        <v>3.247728441496388</v>
+        <v>3.366995305167159</v>
       </c>
       <c r="U77">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y77">
-        <v>7.663516740181368</v>
+        <v>7.451260279145523</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1699442773654375</v>
+        <v>0.1692091888493898</v>
       </c>
       <c r="C78">
-        <v>12.19595404533254</v>
+        <v>11.92266330656553</v>
       </c>
       <c r="D78">
-        <v>24.78195404533254</v>
+        <v>24.85716330656553</v>
       </c>
       <c r="E78">
-        <v>-3.513999999999999</v>
+        <v>-3.165499999999998</v>
       </c>
       <c r="F78">
-        <v>26.486</v>
+        <v>26.8345</v>
       </c>
       <c r="G78">
         <v>13.9</v>
@@ -7671,28 +7671,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M78">
-        <v>1.4381898</v>
+        <v>1.45711335</v>
       </c>
       <c r="N78">
-        <v>9.278136730612244</v>
+        <v>9.259213180612244</v>
       </c>
       <c r="O78">
-        <v>3.247347855714285</v>
+        <v>3.240724613214285</v>
       </c>
       <c r="P78">
-        <v>6.03078887489796</v>
+        <v>6.018488567397959</v>
       </c>
       <c r="Q78">
-        <v>6.130788874897959</v>
+        <v>6.118488567397959</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.596333655689323</v>
+        <v>0.6175306036929991</v>
       </c>
       <c r="T78">
-        <v>3.366995305167159</v>
+        <v>3.496633200461476</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.451260279145523</v>
+        <v>7.354490665130646</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1692091888493898</v>
+        <v>0.168474100333342</v>
       </c>
       <c r="C79">
-        <v>11.92266330656553</v>
+        <v>11.64983045353172</v>
       </c>
       <c r="D79">
-        <v>24.85716330656553</v>
+        <v>24.93283045353172</v>
       </c>
       <c r="E79">
-        <v>-3.165499999999998</v>
+        <v>-2.816999999999997</v>
       </c>
       <c r="F79">
-        <v>26.8345</v>
+        <v>27.183</v>
       </c>
       <c r="G79">
         <v>13.9</v>
@@ -7753,28 +7753,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M79">
-        <v>1.45711335</v>
+        <v>1.4760369</v>
       </c>
       <c r="N79">
-        <v>9.259213180612244</v>
+        <v>9.240289630612244</v>
       </c>
       <c r="O79">
-        <v>3.240724613214285</v>
+        <v>3.234101370714285</v>
       </c>
       <c r="P79">
-        <v>6.018488567397959</v>
+        <v>6.006188259897959</v>
       </c>
       <c r="Q79">
-        <v>6.118488567397959</v>
+        <v>6.106188259897959</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6175306036929991</v>
+        <v>0.6406545469697366</v>
       </c>
       <c r="T79">
-        <v>3.496633200461476</v>
+        <v>3.638056358964367</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.354490665130646</v>
+        <v>7.260202323269996</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.168474100333342</v>
+        <v>0.1677390118172943</v>
       </c>
       <c r="C80">
-        <v>11.64983045353172</v>
+        <v>11.37745968051867</v>
       </c>
       <c r="D80">
-        <v>24.93283045353172</v>
+        <v>25.00895968051867</v>
       </c>
       <c r="E80">
-        <v>-2.816999999999997</v>
+        <v>-2.468499999999999</v>
       </c>
       <c r="F80">
-        <v>27.183</v>
+        <v>27.5315</v>
       </c>
       <c r="G80">
         <v>13.9</v>
@@ -7835,28 +7835,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M80">
-        <v>1.4760369</v>
+        <v>1.49496045</v>
       </c>
       <c r="N80">
-        <v>9.240289630612244</v>
+        <v>9.221366080612244</v>
       </c>
       <c r="O80">
-        <v>3.234101370714285</v>
+        <v>3.227478128214285</v>
       </c>
       <c r="P80">
-        <v>6.006188259897959</v>
+        <v>5.993887952397959</v>
       </c>
       <c r="Q80">
-        <v>6.106188259897959</v>
+        <v>6.093887952397958</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6406545469697366</v>
+        <v>0.6659807705585445</v>
       </c>
       <c r="T80">
-        <v>3.638056358964367</v>
+        <v>3.792948389705629</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.260202323269996</v>
+        <v>7.168301028038731</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1677390118172943</v>
+        <v>0.1670039233012466</v>
       </c>
       <c r="C81">
-        <v>11.37745968051867</v>
+        <v>11.10555523319774</v>
       </c>
       <c r="D81">
-        <v>25.00895968051867</v>
+        <v>25.08555523319774</v>
       </c>
       <c r="E81">
-        <v>-2.468499999999999</v>
+        <v>-2.119999999999997</v>
       </c>
       <c r="F81">
-        <v>27.5315</v>
+        <v>27.88</v>
       </c>
       <c r="G81">
         <v>13.9</v>
@@ -7917,28 +7917,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M81">
-        <v>1.49496045</v>
+        <v>1.513884</v>
       </c>
       <c r="N81">
-        <v>9.221366080612244</v>
+        <v>9.202442530612243</v>
       </c>
       <c r="O81">
-        <v>3.227478128214285</v>
+        <v>3.220854885714285</v>
       </c>
       <c r="P81">
-        <v>5.993887952397959</v>
+        <v>5.981587644897958</v>
       </c>
       <c r="Q81">
-        <v>6.093887952397958</v>
+        <v>6.081587644897958</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6659807705585445</v>
+        <v>0.693839616506233</v>
       </c>
       <c r="T81">
-        <v>3.792948389705629</v>
+        <v>3.963329623521016</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.168301028038731</v>
+        <v>7.078697265188246</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1670039233012466</v>
+        <v>0.1662688347851989</v>
       </c>
       <c r="C82">
-        <v>11.10555523319774</v>
+        <v>10.83412140941336</v>
       </c>
       <c r="D82">
-        <v>25.08555523319774</v>
+        <v>25.16262140941337</v>
       </c>
       <c r="E82">
-        <v>-2.119999999999997</v>
+        <v>-1.771499999999996</v>
       </c>
       <c r="F82">
-        <v>27.88</v>
+        <v>28.2285</v>
       </c>
       <c r="G82">
         <v>13.9</v>
@@ -7999,28 +7999,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M82">
-        <v>1.513884</v>
+        <v>1.53280755</v>
       </c>
       <c r="N82">
-        <v>9.202442530612243</v>
+        <v>9.183518980612245</v>
       </c>
       <c r="O82">
-        <v>3.220854885714285</v>
+        <v>3.214231643214286</v>
       </c>
       <c r="P82">
-        <v>5.981587644897958</v>
+        <v>5.96928733739796</v>
       </c>
       <c r="Q82">
-        <v>6.081587644897958</v>
+        <v>6.069287337397959</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.693839616506233</v>
+        <v>0.7246309725536785</v>
       </c>
       <c r="T82">
-        <v>3.963329623521016</v>
+        <v>4.151645724053814</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>7.078697265188246</v>
+        <v>6.991305940926663</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1662688347851989</v>
+        <v>0.1655337462691511</v>
       </c>
       <c r="C83">
-        <v>10.83412140941336</v>
+        <v>10.56316255998694</v>
       </c>
       <c r="D83">
-        <v>25.16262140941337</v>
+        <v>25.24016255998694</v>
       </c>
       <c r="E83">
-        <v>-1.771499999999996</v>
+        <v>-1.422999999999998</v>
       </c>
       <c r="F83">
-        <v>28.2285</v>
+        <v>28.577</v>
       </c>
       <c r="G83">
         <v>13.9</v>
@@ -8081,28 +8081,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M83">
-        <v>1.53280755</v>
+        <v>1.5517311</v>
       </c>
       <c r="N83">
-        <v>9.183518980612245</v>
+        <v>9.164595430612245</v>
       </c>
       <c r="O83">
-        <v>3.214231643214286</v>
+        <v>3.207608400714285</v>
       </c>
       <c r="P83">
-        <v>5.96928733739796</v>
+        <v>5.956987029897959</v>
       </c>
       <c r="Q83">
-        <v>6.069287337397959</v>
+        <v>6.056987029897959</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7246309725536785</v>
+        <v>0.7588435903841732</v>
       </c>
       <c r="T83">
-        <v>4.151645724053814</v>
+        <v>4.360885835756921</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.991305940926663</v>
+        <v>6.906046112378778</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1655337462691511</v>
+        <v>0.1647986577531034</v>
       </c>
       <c r="C84">
-        <v>10.56316255998694</v>
+        <v>10.29268308953559</v>
       </c>
       <c r="D84">
-        <v>25.24016255998694</v>
+        <v>25.31818308953559</v>
       </c>
       <c r="E84">
-        <v>-1.422999999999998</v>
+        <v>-1.074499999999997</v>
       </c>
       <c r="F84">
-        <v>28.577</v>
+        <v>28.9255</v>
       </c>
       <c r="G84">
         <v>13.9</v>
@@ -8163,28 +8163,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M84">
-        <v>1.5517311</v>
+        <v>1.57065465</v>
       </c>
       <c r="N84">
-        <v>9.164595430612245</v>
+        <v>9.145671880612245</v>
       </c>
       <c r="O84">
-        <v>3.207608400714285</v>
+        <v>3.200985158214285</v>
       </c>
       <c r="P84">
-        <v>5.956987029897959</v>
+        <v>5.944686722397959</v>
       </c>
       <c r="Q84">
-        <v>6.056987029897959</v>
+        <v>6.044686722397959</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7588435903841732</v>
+        <v>0.7970812220770793</v>
       </c>
       <c r="T84">
-        <v>4.360885835756921</v>
+        <v>4.594742431189808</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.906046112378778</v>
+        <v>6.82284073753084</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1647986577531034</v>
+        <v>0.1640635692370557</v>
       </c>
       <c r="C85">
-        <v>10.29268308953559</v>
+        <v>10.02268745730627</v>
       </c>
       <c r="D85">
-        <v>25.31818308953559</v>
+        <v>25.39668745730627</v>
       </c>
       <c r="E85">
-        <v>-1.074499999999997</v>
+        <v>-0.7259999999999955</v>
       </c>
       <c r="F85">
-        <v>28.9255</v>
+        <v>29.274</v>
       </c>
       <c r="G85">
         <v>13.9</v>
@@ -8245,28 +8245,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M85">
-        <v>1.57065465</v>
+        <v>1.5895782</v>
       </c>
       <c r="N85">
-        <v>9.145671880612245</v>
+        <v>9.126748330612244</v>
       </c>
       <c r="O85">
-        <v>3.200985158214285</v>
+        <v>3.194361915714286</v>
       </c>
       <c r="P85">
-        <v>5.944686722397959</v>
+        <v>5.932386414897959</v>
       </c>
       <c r="Q85">
-        <v>6.044686722397959</v>
+        <v>6.032386414897958</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7970812220770793</v>
+        <v>0.8400985577315985</v>
       </c>
       <c r="T85">
-        <v>4.594742431189808</v>
+        <v>4.857831101051803</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.82284073753084</v>
+        <v>6.741616443036425</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1640635692370557</v>
+        <v>0.163328480721008</v>
       </c>
       <c r="C86">
-        <v>10.02268745730627</v>
+        <v>9.753180178025257</v>
       </c>
       <c r="D86">
-        <v>25.39668745730627</v>
+        <v>25.47568017802525</v>
       </c>
       <c r="E86">
-        <v>-0.7259999999999991</v>
+        <v>-0.3775000000000013</v>
       </c>
       <c r="F86">
-        <v>29.274</v>
+        <v>29.6225</v>
       </c>
       <c r="G86">
         <v>13.9</v>
@@ -8327,28 +8327,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M86">
-        <v>1.5895782</v>
+        <v>1.60850175</v>
       </c>
       <c r="N86">
-        <v>9.126748330612244</v>
+        <v>9.107824780612244</v>
       </c>
       <c r="O86">
-        <v>3.194361915714286</v>
+        <v>3.187738673214285</v>
       </c>
       <c r="P86">
-        <v>5.932386414897959</v>
+        <v>5.920086107397958</v>
       </c>
       <c r="Q86">
-        <v>6.032386414897958</v>
+        <v>6.020086107397958</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8400985577315979</v>
+        <v>0.8888515381400532</v>
       </c>
       <c r="T86">
-        <v>4.8578311010518</v>
+        <v>5.15599826022873</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.741616443036426</v>
+        <v>6.662303308412468</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.163328480721008</v>
+        <v>0.1625933922049603</v>
       </c>
       <c r="C87">
-        <v>9.753180178025257</v>
+        <v>9.484165822763703</v>
       </c>
       <c r="D87">
-        <v>25.47568017802525</v>
+        <v>25.5551658227637</v>
       </c>
       <c r="E87">
-        <v>-0.3775000000000013</v>
+        <v>-0.02899999999999991</v>
       </c>
       <c r="F87">
-        <v>29.6225</v>
+        <v>29.971</v>
       </c>
       <c r="G87">
         <v>13.9</v>
@@ -8409,28 +8409,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M87">
-        <v>1.60850175</v>
+        <v>1.6274253</v>
       </c>
       <c r="N87">
-        <v>9.107824780612244</v>
+        <v>9.088901230612244</v>
       </c>
       <c r="O87">
-        <v>3.187738673214285</v>
+        <v>3.181115430714285</v>
       </c>
       <c r="P87">
-        <v>5.920086107397958</v>
+        <v>5.907785799897958</v>
       </c>
       <c r="Q87">
-        <v>6.020086107397958</v>
+        <v>6.007785799897958</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8888515381400532</v>
+        <v>0.9445692300354304</v>
       </c>
       <c r="T87">
-        <v>5.15599826022873</v>
+        <v>5.496760727859504</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.662303308412468</v>
+        <v>6.584834665291392</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1625933922049603</v>
+        <v>0.1618583036889125</v>
       </c>
       <c r="C88">
-        <v>9.484165822763703</v>
+        <v>9.215649019819384</v>
       </c>
       <c r="D88">
-        <v>25.5551658227637</v>
+        <v>25.63514901981939</v>
       </c>
       <c r="E88">
-        <v>-0.02899999999999991</v>
+        <v>0.3195000000000014</v>
       </c>
       <c r="F88">
-        <v>29.971</v>
+        <v>30.3195</v>
       </c>
       <c r="G88">
         <v>13.9</v>
@@ -8491,28 +8491,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M88">
-        <v>1.6274253</v>
+        <v>1.64634885</v>
       </c>
       <c r="N88">
-        <v>9.088901230612244</v>
+        <v>9.069977680612244</v>
       </c>
       <c r="O88">
-        <v>3.181115430714285</v>
+        <v>3.174492188214285</v>
       </c>
       <c r="P88">
-        <v>5.907785799897958</v>
+        <v>5.895485492397959</v>
       </c>
       <c r="Q88">
-        <v>6.007785799897958</v>
+        <v>5.995485492397958</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9445692300354304</v>
+        <v>1.008858874530096</v>
       </c>
       <c r="T88">
-        <v>5.496760727859504</v>
+        <v>5.889948190510398</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.584834665291392</v>
+        <v>6.509146910517928</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1618583036889125</v>
+        <v>0.1611232151728648</v>
       </c>
       <c r="C89">
-        <v>9.215649019819384</v>
+        <v>8.947634455615042</v>
       </c>
       <c r="D89">
-        <v>25.63514901981939</v>
+        <v>25.71563445561505</v>
       </c>
       <c r="E89">
-        <v>0.3195000000000014</v>
+        <v>0.6680000000000028</v>
       </c>
       <c r="F89">
-        <v>30.3195</v>
+        <v>30.668</v>
       </c>
       <c r="G89">
         <v>13.9</v>
@@ -8573,28 +8573,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M89">
-        <v>1.64634885</v>
+        <v>1.6652724</v>
       </c>
       <c r="N89">
-        <v>9.069977680612244</v>
+        <v>9.051054130612243</v>
       </c>
       <c r="O89">
-        <v>3.174492188214285</v>
+        <v>3.167868945714285</v>
       </c>
       <c r="P89">
-        <v>5.895485492397959</v>
+        <v>5.883185184897958</v>
       </c>
       <c r="Q89">
-        <v>5.995485492397958</v>
+        <v>5.983185184897958</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.008858874530096</v>
+        <v>1.083863459773873</v>
       </c>
       <c r="T89">
-        <v>5.889948190510398</v>
+        <v>6.348666896936443</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.509146910517928</v>
+        <v>6.435179331989315</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1611232151728648</v>
+        <v>0.1603881266568171</v>
       </c>
       <c r="C90">
-        <v>8.947634455615042</v>
+        <v>8.680126875613709</v>
       </c>
       <c r="D90">
-        <v>25.71563445561505</v>
+        <v>25.79662687561371</v>
       </c>
       <c r="E90">
-        <v>0.6680000000000028</v>
+        <v>1.016500000000001</v>
       </c>
       <c r="F90">
-        <v>30.668</v>
+        <v>31.0165</v>
       </c>
       <c r="G90">
         <v>13.9</v>
@@ -8655,28 +8655,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M90">
-        <v>1.6652724</v>
+        <v>1.68419595</v>
       </c>
       <c r="N90">
-        <v>9.051054130612243</v>
+        <v>9.032130580612245</v>
       </c>
       <c r="O90">
-        <v>3.167868945714285</v>
+        <v>3.161245703214286</v>
       </c>
       <c r="P90">
-        <v>5.883185184897958</v>
+        <v>5.870884877397959</v>
       </c>
       <c r="Q90">
-        <v>5.983185184897958</v>
+        <v>5.970884877397959</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.083863459773873</v>
+        <v>1.172505242334701</v>
       </c>
       <c r="T90">
-        <v>6.348666896936443</v>
+        <v>6.890789004530857</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.435179331989315</v>
+        <v>6.362873946236626</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1603881266568171</v>
+        <v>0.1596530381407693</v>
       </c>
       <c r="C91">
-        <v>8.680126875613709</v>
+        <v>8.413131085251429</v>
       </c>
       <c r="D91">
-        <v>25.79662687561371</v>
+        <v>25.87813108525143</v>
       </c>
       <c r="E91">
-        <v>1.016500000000001</v>
+        <v>1.365000000000002</v>
       </c>
       <c r="F91">
-        <v>31.0165</v>
+        <v>31.365</v>
       </c>
       <c r="G91">
         <v>13.9</v>
@@ -8737,28 +8737,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M91">
-        <v>1.68419595</v>
+        <v>1.7031195</v>
       </c>
       <c r="N91">
-        <v>9.032130580612245</v>
+        <v>9.013207030612245</v>
       </c>
       <c r="O91">
-        <v>3.161245703214286</v>
+        <v>3.154622460714286</v>
       </c>
       <c r="P91">
-        <v>5.870884877397959</v>
+        <v>5.858584569897959</v>
       </c>
       <c r="Q91">
-        <v>5.970884877397959</v>
+        <v>5.958584569897958</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.172505242334701</v>
+        <v>1.278875381407694</v>
       </c>
       <c r="T91">
-        <v>6.890789004530857</v>
+        <v>7.541335533644157</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.362873946236626</v>
+        <v>6.292175346833997</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1596530381407693</v>
+        <v>0.1589179496247216</v>
       </c>
       <c r="C92">
-        <v>8.413131085251429</v>
+        <v>8.146651950887637</v>
       </c>
       <c r="D92">
-        <v>25.87813108525143</v>
+        <v>25.96015195088764</v>
       </c>
       <c r="E92">
-        <v>1.365000000000002</v>
+        <v>1.713500000000003</v>
       </c>
       <c r="F92">
-        <v>31.365</v>
+        <v>31.7135</v>
       </c>
       <c r="G92">
         <v>13.9</v>
@@ -8819,28 +8819,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M92">
-        <v>1.7031195</v>
+        <v>1.72204305</v>
       </c>
       <c r="N92">
-        <v>9.013207030612245</v>
+        <v>8.994283480612244</v>
       </c>
       <c r="O92">
-        <v>3.154622460714286</v>
+        <v>3.147999218214285</v>
       </c>
       <c r="P92">
-        <v>5.858584569897959</v>
+        <v>5.846284262397959</v>
       </c>
       <c r="Q92">
-        <v>5.958584569897958</v>
+        <v>5.946284262397959</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.278875381407694</v>
+        <v>1.408883329163574</v>
       </c>
       <c r="T92">
-        <v>7.541335533644157</v>
+        <v>8.336447958115967</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.292175346833997</v>
+        <v>6.223030562802855</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1589179496247216</v>
+        <v>0.1581828611086739</v>
       </c>
       <c r="C93">
-        <v>8.146651950887637</v>
+        <v>7.880694400773741</v>
       </c>
       <c r="D93">
-        <v>25.96015195088764</v>
+        <v>26.04269440077375</v>
       </c>
       <c r="E93">
-        <v>1.713500000000003</v>
+        <v>2.062000000000005</v>
       </c>
       <c r="F93">
-        <v>31.7135</v>
+        <v>32.062</v>
       </c>
       <c r="G93">
         <v>13.9</v>
@@ -8901,28 +8901,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M93">
-        <v>1.72204305</v>
+        <v>1.7409666</v>
       </c>
       <c r="N93">
-        <v>8.994283480612244</v>
+        <v>8.975359930612244</v>
       </c>
       <c r="O93">
-        <v>3.147999218214285</v>
+        <v>3.141375975714285</v>
       </c>
       <c r="P93">
-        <v>5.846284262397959</v>
+        <v>5.833983954897959</v>
       </c>
       <c r="Q93">
-        <v>5.946284262397959</v>
+        <v>5.933983954897958</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.408883329163574</v>
+        <v>1.571393263858424</v>
       </c>
       <c r="T93">
-        <v>8.336447958115967</v>
+        <v>9.330338488705729</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.223030562802855</v>
+        <v>6.155388926250649</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1581828611086739</v>
+        <v>0.1580522725926262</v>
       </c>
       <c r="C94">
-        <v>7.880694400773741</v>
+        <v>7.546913009824344</v>
       </c>
       <c r="D94">
-        <v>26.04269440077375</v>
+        <v>26.05741300982435</v>
       </c>
       <c r="E94">
-        <v>2.062000000000005</v>
+        <v>2.410500000000006</v>
       </c>
       <c r="F94">
-        <v>32.062</v>
+        <v>32.41050000000001</v>
       </c>
       <c r="G94">
         <v>13.9</v>
@@ -8983,45 +8983,45 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M94">
-        <v>1.7409666</v>
+        <v>1.79230065</v>
       </c>
       <c r="N94">
-        <v>8.975359930612244</v>
+        <v>8.924025880612245</v>
       </c>
       <c r="O94">
-        <v>3.141375975714285</v>
+        <v>3.123409058214285</v>
       </c>
       <c r="P94">
-        <v>5.833983954897959</v>
+        <v>5.800616822397959</v>
       </c>
       <c r="Q94">
-        <v>5.933983954897958</v>
+        <v>5.900616822397959</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.571393263858424</v>
+        <v>1.780334608466089</v>
       </c>
       <c r="T94">
-        <v>9.330338488705729</v>
+        <v>10.60819774232114</v>
       </c>
       <c r="U94">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V94">
         <v>0.35</v>
       </c>
       <c r="W94">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>6.155388926250649</v>
+        <v>5.979089797580691</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1580522725926262</v>
+        <v>0.1573236840765784</v>
       </c>
       <c r="C95">
-        <v>7.546913009824344</v>
+        <v>7.280838414625357</v>
       </c>
       <c r="D95">
-        <v>26.05741300982435</v>
+        <v>26.13983841462536</v>
       </c>
       <c r="E95">
-        <v>2.410500000000006</v>
+        <v>2.759</v>
       </c>
       <c r="F95">
-        <v>32.41050000000001</v>
+        <v>32.759</v>
       </c>
       <c r="G95">
         <v>13.9</v>
@@ -9065,28 +9065,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M95">
-        <v>1.79230065</v>
+        <v>1.8115727</v>
       </c>
       <c r="N95">
-        <v>8.924025880612245</v>
+        <v>8.904753830612243</v>
       </c>
       <c r="O95">
-        <v>3.123409058214285</v>
+        <v>3.116663840714285</v>
       </c>
       <c r="P95">
-        <v>5.800616822397959</v>
+        <v>5.788089989897959</v>
       </c>
       <c r="Q95">
-        <v>5.900616822397959</v>
+        <v>5.888089989897958</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.780334608466089</v>
+        <v>2.058923067942976</v>
       </c>
       <c r="T95">
-        <v>10.60819774232114</v>
+        <v>12.31201008047502</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.979089797580691</v>
+        <v>5.915482459308557</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1573236840765784</v>
+        <v>0.1565950955605307</v>
       </c>
       <c r="C96">
-        <v>7.280838414625357</v>
+        <v>7.015286934005665</v>
       </c>
       <c r="D96">
-        <v>26.13983841462536</v>
+        <v>26.22278693400566</v>
       </c>
       <c r="E96">
-        <v>2.759</v>
+        <v>3.107500000000002</v>
       </c>
       <c r="F96">
-        <v>32.759</v>
+        <v>33.1075</v>
       </c>
       <c r="G96">
         <v>13.9</v>
@@ -9147,28 +9147,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M96">
-        <v>1.8115727</v>
+        <v>1.83084475</v>
       </c>
       <c r="N96">
-        <v>8.904753830612243</v>
+        <v>8.885481780612244</v>
       </c>
       <c r="O96">
-        <v>3.116663840714285</v>
+        <v>3.109918623214285</v>
       </c>
       <c r="P96">
-        <v>5.788089989897959</v>
+        <v>5.775563157397959</v>
       </c>
       <c r="Q96">
-        <v>5.888089989897958</v>
+        <v>5.875563157397958</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.058923067942976</v>
+        <v>2.448946911210617</v>
       </c>
       <c r="T96">
-        <v>12.31201008047502</v>
+        <v>14.69734735389046</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.915482459308557</v>
+        <v>5.853214222894783</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1565950955605307</v>
+        <v>0.155866507044483</v>
       </c>
       <c r="C97">
-        <v>7.015286934005665</v>
+        <v>6.750263563754864</v>
       </c>
       <c r="D97">
-        <v>26.22278693400566</v>
+        <v>26.30626356375487</v>
       </c>
       <c r="E97">
-        <v>3.107500000000002</v>
+        <v>3.456000000000003</v>
       </c>
       <c r="F97">
-        <v>33.1075</v>
+        <v>33.456</v>
       </c>
       <c r="G97">
         <v>13.9</v>
@@ -9229,28 +9229,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M97">
-        <v>1.83084475</v>
+        <v>1.8501168</v>
       </c>
       <c r="N97">
-        <v>8.885481780612244</v>
+        <v>8.866209730612244</v>
       </c>
       <c r="O97">
-        <v>3.109918623214285</v>
+        <v>3.103173405714285</v>
       </c>
       <c r="P97">
-        <v>5.775563157397959</v>
+        <v>5.763036324897959</v>
       </c>
       <c r="Q97">
-        <v>5.875563157397958</v>
+        <v>5.863036324897958</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.448946911210617</v>
+        <v>3.03398267611208</v>
       </c>
       <c r="T97">
-        <v>14.69734735389046</v>
+        <v>18.27535326401361</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.853214222894783</v>
+        <v>5.792243241406295</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.155866507044483</v>
+        <v>0.1551379185284353</v>
       </c>
       <c r="C98">
-        <v>6.750263563754856</v>
+        <v>6.485773363479332</v>
       </c>
       <c r="D98">
-        <v>26.30626356375486</v>
+        <v>26.39027336347933</v>
       </c>
       <c r="E98">
-        <v>3.456000000000003</v>
+        <v>3.804499999999997</v>
       </c>
       <c r="F98">
-        <v>33.456</v>
+        <v>33.8045</v>
       </c>
       <c r="G98">
         <v>13.9</v>
@@ -9311,28 +9311,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M98">
-        <v>1.8501168</v>
+        <v>1.86938885</v>
       </c>
       <c r="N98">
-        <v>8.866209730612244</v>
+        <v>8.846937680612244</v>
       </c>
       <c r="O98">
-        <v>3.103173405714285</v>
+        <v>3.096428188214285</v>
       </c>
       <c r="P98">
-        <v>5.763036324897959</v>
+        <v>5.750509492397959</v>
       </c>
       <c r="Q98">
-        <v>5.863036324897958</v>
+        <v>5.850509492397959</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.033982676112073</v>
+        <v>4.009042284281173</v>
       </c>
       <c r="T98">
-        <v>18.27535326401356</v>
+        <v>24.23869644755212</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.792243241406295</v>
+        <v>5.732529393556747</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1551379185284353</v>
+        <v>0.1544093300123875</v>
       </c>
       <c r="C99">
-        <v>6.485773363479332</v>
+        <v>6.221821457624515</v>
       </c>
       <c r="D99">
-        <v>26.39027336347933</v>
+        <v>26.47482145762451</v>
       </c>
       <c r="E99">
-        <v>3.804499999999997</v>
+        <v>4.152999999999999</v>
       </c>
       <c r="F99">
-        <v>33.8045</v>
+        <v>34.153</v>
       </c>
       <c r="G99">
         <v>13.9</v>
@@ -9393,28 +9393,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M99">
-        <v>1.86938885</v>
+        <v>1.8886609</v>
       </c>
       <c r="N99">
-        <v>8.846937680612244</v>
+        <v>8.827665630612245</v>
       </c>
       <c r="O99">
-        <v>3.096428188214285</v>
+        <v>3.089682970714286</v>
       </c>
       <c r="P99">
-        <v>5.750509492397959</v>
+        <v>5.737982659897959</v>
       </c>
       <c r="Q99">
-        <v>5.850509492397959</v>
+        <v>5.837982659897959</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.009042284281173</v>
+        <v>5.959161500619372</v>
       </c>
       <c r="T99">
-        <v>24.23869644755212</v>
+        <v>36.16538281462924</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.732529393556747</v>
+        <v>5.67403419566331</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1544093300123875</v>
+        <v>0.1536807414963398</v>
       </c>
       <c r="C100">
-        <v>6.221821457624515</v>
+        <v>5.958413036516859</v>
       </c>
       <c r="D100">
-        <v>26.47482145762451</v>
+        <v>26.55991303651686</v>
       </c>
       <c r="E100">
-        <v>4.152999999999999</v>
+        <v>4.5015</v>
       </c>
       <c r="F100">
-        <v>34.153</v>
+        <v>34.5015</v>
       </c>
       <c r="G100">
         <v>13.9</v>
@@ -9475,28 +9475,28 @@
         <v>10.71632653061224</v>
       </c>
       <c r="M100">
-        <v>1.8886609</v>
+        <v>1.90793295</v>
       </c>
       <c r="N100">
-        <v>8.827665630612245</v>
+        <v>8.808393580612245</v>
       </c>
       <c r="O100">
-        <v>3.089682970714286</v>
+        <v>3.082937753214285</v>
       </c>
       <c r="P100">
-        <v>5.737982659897959</v>
+        <v>5.72545582739796</v>
       </c>
       <c r="Q100">
-        <v>5.837982659897959</v>
+        <v>5.82545582739796</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.959161500619372</v>
+        <v>11.80951914963397</v>
       </c>
       <c r="T100">
-        <v>36.16538281462924</v>
+        <v>71.94544191586061</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.67403419566331</v>
+        <v>5.616720718939439</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1536807414963398</v>
-      </c>
-      <c r="C101">
-        <v>5.958413036516859</v>
-      </c>
-      <c r="D101">
-        <v>26.55991303651686</v>
-      </c>
-      <c r="E101">
-        <v>4.5015</v>
-      </c>
-      <c r="F101">
-        <v>34.5015</v>
-      </c>
-      <c r="G101">
-        <v>13.9</v>
-      </c>
-      <c r="H101">
-        <v>4.85</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.81632653061224</v>
-      </c>
-      <c r="K101">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="L101">
-        <v>10.71632653061224</v>
-      </c>
-      <c r="M101">
-        <v>1.90793295</v>
-      </c>
-      <c r="N101">
-        <v>8.808393580612245</v>
-      </c>
-      <c r="O101">
-        <v>3.082937753214285</v>
-      </c>
-      <c r="P101">
-        <v>5.72545582739796</v>
-      </c>
-      <c r="Q101">
-        <v>5.82545582739796</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.80951914963397</v>
-      </c>
-      <c r="T101">
-        <v>71.94544191586061</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.616720718939439</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
